--- a/app/static/storage/May 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/May 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B674CC-1536-40B5-8B02-26654C4D178D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183FD637-68CF-40A8-B83A-C246E15B3793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -740,9 +740,6 @@
     <t>HRS. OF FLOCERPIDA A. SAAGUNDO, REP BY FLORLITA SAAGUNDO ASIO VS. TIRSO CANATOY, JR.</t>
   </si>
   <si>
-    <t>THE HRS OF RAYMUNDO RACZA NAMELY: ISIDRO RACAZA. GEMMA RACAZ MALIWAT, CAMELO RACAZA, PETRONNELO RACAZA, ARCADIO RACAZA JR., AND THE HRS. OF BENJAMIN RACAZA NAMELY: AGNES BALANSAG RACAZA VS. ROBERTO BANGAHON, ROMEO GERALDO, JULIUS LAHOY</t>
-  </si>
-  <si>
     <t>HON.SAIDAMEN M. GANIA</t>
   </si>
   <si>
@@ -762,6 +759,9 @@
   </si>
   <si>
     <t>CLERK  II</t>
+  </si>
+  <si>
+    <t>PP vs. Arvin Wong Orihuela</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="133">
+  <borders count="135">
     <border>
       <left/>
       <right/>
@@ -1753,21 +1753,6 @@
         <color indexed="8"/>
       </right>
       <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="hair">
@@ -2701,11 +2686,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="344">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2995,23 +3023,11 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -3030,19 +3046,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3056,19 +3072,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3080,7 +3096,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3088,56 +3104,56 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3148,24 +3164,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3177,7 +3193,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3187,26 +3203,30 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3220,12 +3240,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3235,12 +3255,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3250,95 +3270,252 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="107" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="132" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3346,174 +3523,13 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3529,6 +3545,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="132" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="133" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4016,23 +4066,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="288" t="s">
+      <c r="A3" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="289"/>
-      <c r="E3" s="289"/>
-      <c r="F3" s="289"/>
-      <c r="G3" s="289"/>
-      <c r="H3" s="289"/>
-      <c r="I3" s="289"/>
-      <c r="J3" s="289"/>
-      <c r="K3" s="289"/>
-      <c r="L3" s="289"/>
-      <c r="M3" s="289"/>
-      <c r="N3" s="289"/>
-      <c r="O3" s="289"/>
+      <c r="B3" s="291"/>
+      <c r="C3" s="291"/>
+      <c r="D3" s="291"/>
+      <c r="E3" s="291"/>
+      <c r="F3" s="291"/>
+      <c r="G3" s="291"/>
+      <c r="H3" s="291"/>
+      <c r="I3" s="291"/>
+      <c r="J3" s="291"/>
+      <c r="K3" s="291"/>
+      <c r="L3" s="291"/>
+      <c r="M3" s="291"/>
+      <c r="N3" s="291"/>
+      <c r="O3" s="291"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -4043,20 +4093,20 @@
       <c r="A4" s="293" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="289"/>
-      <c r="C4" s="289"/>
-      <c r="D4" s="289"/>
-      <c r="E4" s="289"/>
-      <c r="F4" s="289"/>
-      <c r="G4" s="289"/>
-      <c r="H4" s="289"/>
-      <c r="I4" s="289"/>
-      <c r="J4" s="289"/>
-      <c r="K4" s="289"/>
-      <c r="L4" s="289"/>
-      <c r="M4" s="289"/>
-      <c r="N4" s="289"/>
-      <c r="O4" s="289"/>
+      <c r="B4" s="291"/>
+      <c r="C4" s="291"/>
+      <c r="D4" s="291"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
+      <c r="I4" s="291"/>
+      <c r="J4" s="291"/>
+      <c r="K4" s="291"/>
+      <c r="L4" s="291"/>
+      <c r="M4" s="291"/>
+      <c r="N4" s="291"/>
+      <c r="O4" s="291"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -4081,62 +4131,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="282" t="s">
+      <c r="A6" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="284"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="E6" s="294" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="295"/>
-      <c r="G6" s="295"/>
-      <c r="H6" s="295"/>
-      <c r="I6" s="295"/>
-      <c r="J6" s="295"/>
-      <c r="K6" s="295"/>
-      <c r="L6" s="295"/>
-      <c r="M6" s="295"/>
-      <c r="N6" s="295"/>
-      <c r="O6" s="259"/>
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
+      <c r="H6" s="270"/>
+      <c r="I6" s="270"/>
+      <c r="J6" s="270"/>
+      <c r="K6" s="270"/>
+      <c r="L6" s="270"/>
+      <c r="M6" s="270"/>
+      <c r="N6" s="270"/>
+      <c r="O6" s="238"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="285"/>
-      <c r="B7" s="286"/>
-      <c r="C7" s="286"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="276" t="s">
+      <c r="A7" s="256"/>
+      <c r="B7" s="257"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="273" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="260" t="s">
+      <c r="G7" s="273" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="263" t="s">
+      <c r="H7" s="240" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="263" t="s">
+      <c r="I7" s="240" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="263" t="s">
+      <c r="J7" s="240" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="260" t="s">
+      <c r="K7" s="273" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="260" t="s">
+      <c r="L7" s="273" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="263" t="s">
+      <c r="M7" s="240" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="279" t="s">
+      <c r="N7" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="296" t="s">
+      <c r="O7" s="295" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4147,17 +4197,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="277"/>
-      <c r="F8" s="261"/>
-      <c r="G8" s="261"/>
-      <c r="H8" s="261"/>
-      <c r="I8" s="261"/>
-      <c r="J8" s="261"/>
-      <c r="K8" s="261"/>
-      <c r="L8" s="261"/>
-      <c r="M8" s="261"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="292"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="288"/>
+      <c r="O8" s="261"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4168,86 +4218,86 @@
       <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="277"/>
-      <c r="F9" s="261"/>
-      <c r="G9" s="261"/>
-      <c r="H9" s="261"/>
-      <c r="I9" s="261"/>
-      <c r="J9" s="261"/>
-      <c r="K9" s="261"/>
-      <c r="L9" s="261"/>
-      <c r="M9" s="261"/>
-      <c r="N9" s="280"/>
-      <c r="O9" s="292"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="288"/>
+      <c r="O9" s="261"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="266" t="s">
+      <c r="A10" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="267"/>
-      <c r="C10" s="268"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="277"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="261"/>
-      <c r="H10" s="261"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="261"/>
-      <c r="K10" s="261"/>
-      <c r="L10" s="261"/>
-      <c r="M10" s="261"/>
-      <c r="N10" s="280"/>
-      <c r="O10" s="292"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="288"/>
+      <c r="O10" s="261"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="266" t="s">
+      <c r="A11" s="244" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="267"/>
-      <c r="C11" s="268"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="246"/>
       <c r="D11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="277"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="261"/>
-      <c r="H11" s="261"/>
-      <c r="I11" s="261"/>
-      <c r="J11" s="261"/>
-      <c r="K11" s="261"/>
-      <c r="L11" s="261"/>
-      <c r="M11" s="261"/>
-      <c r="N11" s="280"/>
-      <c r="O11" s="292"/>
+      <c r="E11" s="285"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="288"/>
+      <c r="O11" s="261"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="266" t="s">
+      <c r="A12" s="244" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="267"/>
-      <c r="C12" s="268"/>
+      <c r="B12" s="245"/>
+      <c r="C12" s="246"/>
       <c r="D12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="278"/>
-      <c r="F12" s="262"/>
-      <c r="G12" s="262"/>
-      <c r="H12" s="262"/>
-      <c r="I12" s="262"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="262"/>
-      <c r="N12" s="281"/>
-      <c r="O12" s="287"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="242"/>
+      <c r="J12" s="242"/>
+      <c r="K12" s="242"/>
+      <c r="L12" s="242"/>
+      <c r="M12" s="242"/>
+      <c r="N12" s="289"/>
+      <c r="O12" s="258"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="290"/>
-      <c r="B13" s="291"/>
-      <c r="C13" s="291"/>
-      <c r="D13" s="292"/>
+      <c r="A13" s="259"/>
+      <c r="B13" s="292"/>
+      <c r="C13" s="292"/>
+      <c r="D13" s="261"/>
       <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
@@ -4289,42 +4339,42 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="297" t="s">
+      <c r="C14" s="243" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="259"/>
-      <c r="E14" s="208">
-        <v>0</v>
-      </c>
-      <c r="F14" s="208">
-        <v>0</v>
-      </c>
-      <c r="G14" s="208">
+      <c r="D14" s="238"/>
+      <c r="E14" s="204">
+        <v>0</v>
+      </c>
+      <c r="F14" s="204">
+        <v>0</v>
+      </c>
+      <c r="G14" s="204">
         <v>12</v>
       </c>
-      <c r="H14" s="208">
-        <v>0</v>
-      </c>
-      <c r="I14" s="208">
-        <v>0</v>
-      </c>
-      <c r="J14" s="208">
+      <c r="H14" s="204">
+        <v>0</v>
+      </c>
+      <c r="I14" s="204">
+        <v>0</v>
+      </c>
+      <c r="J14" s="204">
         <v>2</v>
       </c>
-      <c r="K14" s="208">
-        <v>0</v>
-      </c>
-      <c r="L14" s="208">
-        <v>0</v>
-      </c>
-      <c r="M14" s="208">
-        <v>0</v>
-      </c>
-      <c r="N14" s="208">
+      <c r="K14" s="204">
+        <v>0</v>
+      </c>
+      <c r="L14" s="204">
+        <v>0</v>
+      </c>
+      <c r="M14" s="204">
+        <v>0</v>
+      </c>
+      <c r="N14" s="204">
         <v>6</v>
       </c>
-      <c r="O14" s="221">
-        <f t="shared" ref="O14:O25" si="0">SUM(E14:N14)</f>
+      <c r="O14" s="217">
+        <f t="shared" ref="O14:O24" si="0">SUM(E14:N14)</f>
         <v>20</v>
       </c>
     </row>
@@ -4335,185 +4385,185 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="275" t="s">
+      <c r="C15" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="E15" s="208">
+      <c r="D15" s="238"/>
+      <c r="E15" s="204">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="213">
+      <c r="F15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="213">
+      <c r="G15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H15" s="213">
+      <c r="H15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="213">
+      <c r="I15" s="209">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J15" s="213">
+      <c r="J15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="213">
+      <c r="K15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="213">
+      <c r="L15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M15" s="213">
+      <c r="M15" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="217">
+      <c r="N15" s="213">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O15" s="222">
+      <c r="O15" s="218">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="270" t="s">
+      <c r="A16" s="278" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="262" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="299"/>
-      <c r="E16" s="209">
-        <v>0</v>
-      </c>
-      <c r="F16" s="214">
-        <v>0</v>
-      </c>
-      <c r="G16" s="214">
-        <v>0</v>
-      </c>
-      <c r="H16" s="214">
-        <v>0</v>
-      </c>
-      <c r="I16" s="214">
-        <v>0</v>
-      </c>
-      <c r="J16" s="214">
-        <v>0</v>
-      </c>
-      <c r="K16" s="214">
-        <v>0</v>
-      </c>
-      <c r="L16" s="214">
-        <v>0</v>
-      </c>
-      <c r="M16" s="214">
-        <v>0</v>
-      </c>
-      <c r="N16" s="218">
+      <c r="D16" s="263"/>
+      <c r="E16" s="205">
+        <v>0</v>
+      </c>
+      <c r="F16" s="210">
+        <v>0</v>
+      </c>
+      <c r="G16" s="210">
+        <v>0</v>
+      </c>
+      <c r="H16" s="210">
+        <v>0</v>
+      </c>
+      <c r="I16" s="210">
+        <v>0</v>
+      </c>
+      <c r="J16" s="210">
+        <v>0</v>
+      </c>
+      <c r="K16" s="210">
+        <v>0</v>
+      </c>
+      <c r="L16" s="210">
+        <v>0</v>
+      </c>
+      <c r="M16" s="210">
+        <v>0</v>
+      </c>
+      <c r="N16" s="214">
         <v>3</v>
       </c>
-      <c r="O16" s="223">
+      <c r="O16" s="219">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="271"/>
+      <c r="A17" s="279"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="264" t="s">
+      <c r="C17" s="275" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="265"/>
-      <c r="E17" s="209">
-        <v>0</v>
-      </c>
-      <c r="F17" s="214">
-        <v>0</v>
-      </c>
-      <c r="G17" s="214">
-        <v>0</v>
-      </c>
-      <c r="H17" s="214">
-        <v>0</v>
-      </c>
-      <c r="I17" s="214">
+      <c r="D17" s="276"/>
+      <c r="E17" s="205">
+        <v>0</v>
+      </c>
+      <c r="F17" s="210">
+        <v>0</v>
+      </c>
+      <c r="G17" s="210">
+        <v>0</v>
+      </c>
+      <c r="H17" s="210">
+        <v>0</v>
+      </c>
+      <c r="I17" s="210">
         <v>1</v>
       </c>
-      <c r="J17" s="214">
-        <v>0</v>
-      </c>
-      <c r="K17" s="214">
-        <v>0</v>
-      </c>
-      <c r="L17" s="214">
-        <v>0</v>
-      </c>
-      <c r="M17" s="214">
-        <v>0</v>
-      </c>
-      <c r="N17" s="218">
-        <v>0</v>
-      </c>
-      <c r="O17" s="224">
+      <c r="J17" s="210">
+        <v>0</v>
+      </c>
+      <c r="K17" s="210">
+        <v>0</v>
+      </c>
+      <c r="L17" s="210">
+        <v>0</v>
+      </c>
+      <c r="M17" s="210">
+        <v>0</v>
+      </c>
+      <c r="N17" s="214">
+        <v>0</v>
+      </c>
+      <c r="O17" s="220">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="272"/>
+      <c r="A18" s="280"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="273" t="s">
+      <c r="C18" s="271" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="274"/>
-      <c r="E18" s="209">
-        <v>0</v>
-      </c>
-      <c r="F18" s="214">
-        <v>0</v>
-      </c>
-      <c r="G18" s="214">
-        <v>0</v>
-      </c>
-      <c r="H18" s="214">
-        <v>0</v>
-      </c>
-      <c r="I18" s="214">
-        <v>0</v>
-      </c>
-      <c r="J18" s="214">
-        <v>0</v>
-      </c>
-      <c r="K18" s="214">
-        <v>0</v>
-      </c>
-      <c r="L18" s="214">
-        <v>0</v>
-      </c>
-      <c r="M18" s="214">
-        <v>0</v>
-      </c>
-      <c r="N18" s="218">
-        <v>0</v>
-      </c>
-      <c r="O18" s="225">
+      <c r="D18" s="272"/>
+      <c r="E18" s="205">
+        <v>0</v>
+      </c>
+      <c r="F18" s="210">
+        <v>0</v>
+      </c>
+      <c r="G18" s="210">
+        <v>0</v>
+      </c>
+      <c r="H18" s="210">
+        <v>0</v>
+      </c>
+      <c r="I18" s="210">
+        <v>0</v>
+      </c>
+      <c r="J18" s="210">
+        <v>0</v>
+      </c>
+      <c r="K18" s="210">
+        <v>0</v>
+      </c>
+      <c r="L18" s="210">
+        <v>0</v>
+      </c>
+      <c r="M18" s="210">
+        <v>0</v>
+      </c>
+      <c r="N18" s="214">
+        <v>0</v>
+      </c>
+      <c r="O18" s="221">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4525,229 +4575,229 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="275" t="s">
+      <c r="C19" s="239" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="E19" s="208">
+      <c r="D19" s="238"/>
+      <c r="E19" s="204">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="213">
+      <c r="F19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G19" s="213">
+      <c r="G19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H19" s="213">
+      <c r="H19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="213">
+      <c r="I19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="213">
+      <c r="J19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K19" s="213">
+      <c r="K19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="213">
+      <c r="L19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M19" s="213">
+      <c r="M19" s="209">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="213">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="218">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="270" t="s">
+      <c r="A20" s="278" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="298" t="s">
+      <c r="C20" s="262" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="299"/>
-      <c r="E20" s="210">
-        <v>0</v>
-      </c>
-      <c r="F20" s="215">
-        <v>0</v>
-      </c>
-      <c r="G20" s="215">
-        <v>0</v>
-      </c>
-      <c r="H20" s="215">
-        <v>0</v>
-      </c>
-      <c r="I20" s="215">
-        <v>0</v>
-      </c>
-      <c r="J20" s="215">
-        <v>0</v>
-      </c>
-      <c r="K20" s="215">
-        <v>0</v>
-      </c>
-      <c r="L20" s="215">
-        <v>0</v>
-      </c>
-      <c r="M20" s="215">
-        <v>0</v>
-      </c>
-      <c r="N20" s="219">
+      <c r="D20" s="263"/>
+      <c r="E20" s="206">
+        <v>0</v>
+      </c>
+      <c r="F20" s="211">
+        <v>0</v>
+      </c>
+      <c r="G20" s="211">
+        <v>0</v>
+      </c>
+      <c r="H20" s="211">
+        <v>0</v>
+      </c>
+      <c r="I20" s="211">
+        <v>0</v>
+      </c>
+      <c r="J20" s="211">
+        <v>0</v>
+      </c>
+      <c r="K20" s="211">
+        <v>0</v>
+      </c>
+      <c r="L20" s="211">
+        <v>0</v>
+      </c>
+      <c r="M20" s="211">
+        <v>0</v>
+      </c>
+      <c r="N20" s="215">
         <v>3</v>
       </c>
-      <c r="O20" s="223">
+      <c r="O20" s="219">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="271"/>
+      <c r="A21" s="279"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="269" t="s">
+      <c r="C21" s="277" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="265"/>
-      <c r="E21" s="209">
-        <v>0</v>
-      </c>
-      <c r="F21" s="214">
-        <v>0</v>
-      </c>
-      <c r="G21" s="214">
-        <v>0</v>
-      </c>
-      <c r="H21" s="214">
-        <v>0</v>
-      </c>
-      <c r="I21" s="214">
-        <v>0</v>
-      </c>
-      <c r="J21" s="214">
-        <v>0</v>
-      </c>
-      <c r="K21" s="214">
-        <v>0</v>
-      </c>
-      <c r="L21" s="214">
-        <v>0</v>
-      </c>
-      <c r="M21" s="214">
-        <v>0</v>
-      </c>
-      <c r="N21" s="218">
-        <v>0</v>
-      </c>
-      <c r="O21" s="224">
+      <c r="D21" s="276"/>
+      <c r="E21" s="205">
+        <v>0</v>
+      </c>
+      <c r="F21" s="210">
+        <v>0</v>
+      </c>
+      <c r="G21" s="210">
+        <v>0</v>
+      </c>
+      <c r="H21" s="210">
+        <v>0</v>
+      </c>
+      <c r="I21" s="210">
+        <v>0</v>
+      </c>
+      <c r="J21" s="210">
+        <v>0</v>
+      </c>
+      <c r="K21" s="210">
+        <v>0</v>
+      </c>
+      <c r="L21" s="210">
+        <v>0</v>
+      </c>
+      <c r="M21" s="210">
+        <v>0</v>
+      </c>
+      <c r="N21" s="214">
+        <v>0</v>
+      </c>
+      <c r="O21" s="220">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="271"/>
+      <c r="A22" s="279"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="264" t="s">
+      <c r="C22" s="275" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="265"/>
-      <c r="E22" s="209">
-        <v>0</v>
-      </c>
-      <c r="F22" s="214">
-        <v>0</v>
-      </c>
-      <c r="G22" s="214">
-        <v>0</v>
-      </c>
-      <c r="H22" s="214">
-        <v>0</v>
-      </c>
-      <c r="I22" s="214">
-        <v>0</v>
-      </c>
-      <c r="J22" s="214">
-        <v>0</v>
-      </c>
-      <c r="K22" s="214">
-        <v>0</v>
-      </c>
-      <c r="L22" s="214">
-        <v>0</v>
-      </c>
-      <c r="M22" s="214">
-        <v>0</v>
-      </c>
-      <c r="N22" s="218">
-        <v>0</v>
-      </c>
-      <c r="O22" s="224">
+      <c r="D22" s="276"/>
+      <c r="E22" s="205">
+        <v>0</v>
+      </c>
+      <c r="F22" s="210">
+        <v>0</v>
+      </c>
+      <c r="G22" s="210">
+        <v>0</v>
+      </c>
+      <c r="H22" s="210">
+        <v>0</v>
+      </c>
+      <c r="I22" s="210">
+        <v>0</v>
+      </c>
+      <c r="J22" s="210">
+        <v>0</v>
+      </c>
+      <c r="K22" s="210">
+        <v>0</v>
+      </c>
+      <c r="L22" s="210">
+        <v>0</v>
+      </c>
+      <c r="M22" s="210">
+        <v>0</v>
+      </c>
+      <c r="N22" s="214">
+        <v>0</v>
+      </c>
+      <c r="O22" s="220">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="272"/>
+      <c r="A23" s="280"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="273" t="s">
+      <c r="C23" s="271" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="274"/>
-      <c r="E23" s="211">
-        <v>0</v>
-      </c>
-      <c r="F23" s="216">
-        <v>0</v>
-      </c>
-      <c r="G23" s="216">
-        <v>0</v>
-      </c>
-      <c r="H23" s="216">
-        <v>0</v>
-      </c>
-      <c r="I23" s="216">
-        <v>0</v>
-      </c>
-      <c r="J23" s="216">
-        <v>0</v>
-      </c>
-      <c r="K23" s="216">
-        <v>0</v>
-      </c>
-      <c r="L23" s="216">
-        <v>0</v>
-      </c>
-      <c r="M23" s="216">
-        <v>0</v>
-      </c>
-      <c r="N23" s="220">
-        <v>0</v>
-      </c>
-      <c r="O23" s="225">
+      <c r="D23" s="272"/>
+      <c r="E23" s="207">
+        <v>0</v>
+      </c>
+      <c r="F23" s="212">
+        <v>0</v>
+      </c>
+      <c r="G23" s="212">
+        <v>0</v>
+      </c>
+      <c r="H23" s="212">
+        <v>0</v>
+      </c>
+      <c r="I23" s="212">
+        <v>0</v>
+      </c>
+      <c r="J23" s="212">
+        <v>0</v>
+      </c>
+      <c r="K23" s="212">
+        <v>0</v>
+      </c>
+      <c r="L23" s="212">
+        <v>0</v>
+      </c>
+      <c r="M23" s="212">
+        <v>0</v>
+      </c>
+      <c r="N23" s="216">
+        <v>0</v>
+      </c>
+      <c r="O23" s="221">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4759,10 +4809,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="258" t="s">
+      <c r="C24" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="259"/>
+      <c r="D24" s="238"/>
       <c r="E24" s="29">
         <f t="shared" ref="E24:M24" si="3">(E14+E15)-E19</f>
         <v>0</v>
@@ -4803,7 +4853,7 @@
         <f>(N14+N15)-N19</f>
         <v>6</v>
       </c>
-      <c r="O24" s="226">
+      <c r="O24" s="222">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -4815,18 +4865,18 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="259"/>
+      <c r="D25" s="238"/>
       <c r="E25" s="41">
         <v>0</v>
       </c>
-      <c r="F25" s="212">
+      <c r="F25" s="208">
         <v>0</v>
       </c>
       <c r="G25" s="41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="41">
         <v>0</v>
@@ -4835,23 +4885,23 @@
         <v>0</v>
       </c>
       <c r="J25" s="41">
+        <v>0</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0</v>
+      </c>
+      <c r="L25" s="41">
+        <v>0</v>
+      </c>
+      <c r="M25" s="42">
+        <v>0</v>
+      </c>
+      <c r="N25" s="42">
         <v>2</v>
       </c>
-      <c r="K25" s="41">
-        <v>0</v>
-      </c>
-      <c r="L25" s="41">
-        <v>0</v>
-      </c>
-      <c r="M25" s="42">
-        <v>0</v>
-      </c>
-      <c r="N25" s="42">
-        <v>7</v>
-      </c>
-      <c r="O25" s="226">
+      <c r="O25" s="222">
         <f>SUM(E25:N25)</f>
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="46" customFormat="1" x14ac:dyDescent="0.2">
@@ -5000,23 +5050,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="L7:L12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="N7:N12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="O7:O12"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="I7:I12"/>
@@ -5033,6 +5066,23 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="N7:N12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="O7:O12"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5088,98 +5138,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="305" t="s">
+      <c r="A3" s="247" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="306"/>
-      <c r="C3" s="306"/>
-      <c r="D3" s="306"/>
-      <c r="E3" s="306"/>
-      <c r="F3" s="306"/>
-      <c r="G3" s="306"/>
-      <c r="H3" s="306"/>
-      <c r="I3" s="306"/>
-      <c r="J3" s="306"/>
-      <c r="K3" s="306"/>
-      <c r="L3" s="307"/>
+      <c r="B3" s="248"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="248"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="249"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="312" t="s">
+      <c r="A4" s="264" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="313"/>
-      <c r="C4" s="313"/>
-      <c r="D4" s="313"/>
-      <c r="E4" s="313"/>
-      <c r="F4" s="313"/>
-      <c r="G4" s="313"/>
-      <c r="H4" s="313"/>
-      <c r="I4" s="313"/>
-      <c r="J4" s="313"/>
-      <c r="K4" s="313"/>
-      <c r="L4" s="314"/>
+      <c r="B4" s="265"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="266"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="308"/>
-      <c r="F5" s="309"/>
-      <c r="G5" s="309"/>
-      <c r="H5" s="309"/>
-      <c r="I5" s="309"/>
-      <c r="J5" s="309"/>
-      <c r="K5" s="309"/>
-      <c r="L5" s="310"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="252"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="282" t="s">
+      <c r="A6" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="284"/>
-      <c r="E6" s="316" t="s">
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
+      <c r="E6" s="269" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="295"/>
-      <c r="G6" s="295"/>
-      <c r="H6" s="295"/>
-      <c r="I6" s="295"/>
-      <c r="J6" s="295"/>
-      <c r="K6" s="259"/>
-      <c r="L6" s="300" t="s">
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
+      <c r="H6" s="270"/>
+      <c r="I6" s="270"/>
+      <c r="J6" s="270"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="274" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="285"/>
-      <c r="B7" s="286"/>
-      <c r="C7" s="286"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="276" t="s">
+      <c r="A7" s="256"/>
+      <c r="B7" s="257"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="284" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="263" t="s">
+      <c r="F7" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="260" t="s">
+      <c r="G7" s="273" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="260" t="s">
+      <c r="H7" s="273" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="260" t="s">
+      <c r="I7" s="273" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="302" t="s">
+      <c r="J7" s="281" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="315" t="s">
+      <c r="K7" s="267" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="301"/>
+      <c r="L7" s="268"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5187,18 +5237,18 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="228">
+      <c r="D8" s="224">
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="277"/>
-      <c r="F8" s="261"/>
-      <c r="G8" s="261"/>
-      <c r="H8" s="261"/>
-      <c r="I8" s="261"/>
-      <c r="J8" s="303"/>
-      <c r="K8" s="301"/>
-      <c r="L8" s="301"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="282"/>
+      <c r="K8" s="268"/>
+      <c r="L8" s="268"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5210,77 +5260,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="277"/>
-      <c r="F9" s="261"/>
-      <c r="G9" s="261"/>
-      <c r="H9" s="261"/>
-      <c r="I9" s="261"/>
-      <c r="J9" s="303"/>
-      <c r="K9" s="301"/>
-      <c r="L9" s="301"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="282"/>
+      <c r="K9" s="268"/>
+      <c r="L9" s="268"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="266" t="s">
+      <c r="A10" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="267"/>
-      <c r="C10" s="268"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="277"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="261"/>
-      <c r="H10" s="261"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="303"/>
-      <c r="K10" s="301"/>
-      <c r="L10" s="301"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="282"/>
+      <c r="K10" s="268"/>
+      <c r="L10" s="268"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="266" t="s">
+      <c r="A11" s="244" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="267"/>
-      <c r="C11" s="268"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="246"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="277"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="261"/>
-      <c r="H11" s="261"/>
-      <c r="I11" s="261"/>
-      <c r="J11" s="303"/>
-      <c r="K11" s="301"/>
-      <c r="L11" s="301"/>
+      <c r="E11" s="285"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="282"/>
+      <c r="K11" s="268"/>
+      <c r="L11" s="268"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="266" t="s">
+      <c r="A12" s="244" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="267"/>
-      <c r="C12" s="268"/>
-      <c r="D12" s="227" t="str">
+      <c r="B12" s="245"/>
+      <c r="C12" s="246"/>
+      <c r="D12" s="223" t="str">
         <f>'Page 1'!D12</f>
         <v>May 2026</v>
       </c>
-      <c r="E12" s="278"/>
-      <c r="F12" s="262"/>
-      <c r="G12" s="262"/>
-      <c r="H12" s="262"/>
-      <c r="I12" s="262"/>
-      <c r="J12" s="304"/>
-      <c r="K12" s="301"/>
-      <c r="L12" s="301"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="242"/>
+      <c r="J12" s="283"/>
+      <c r="K12" s="268"/>
+      <c r="L12" s="268"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="290"/>
-      <c r="B13" s="311"/>
-      <c r="C13" s="311"/>
-      <c r="D13" s="292"/>
+      <c r="A13" s="259"/>
+      <c r="B13" s="260"/>
+      <c r="C13" s="260"/>
+      <c r="D13" s="261"/>
       <c r="E13" s="73" t="s">
         <v>81</v>
       </c>
@@ -5313,10 +5363,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="297" t="s">
+      <c r="C14" s="243" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="259"/>
+      <c r="D14" s="238"/>
       <c r="E14" s="28">
         <v>1</v>
       </c>
@@ -5339,7 +5389,7 @@
         <f t="shared" ref="K14:K24" si="0">SUM(E14:J14)</f>
         <v>10</v>
       </c>
-      <c r="L14" s="229">
+      <c r="L14" s="225">
         <f>'Page 1'!O14+'Page 2'!K14</f>
         <v>30</v>
       </c>
@@ -5351,10 +5401,10 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="275" t="s">
+      <c r="C15" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="259"/>
+      <c r="D15" s="238"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>5</v>
@@ -5383,22 +5433,22 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L15" s="229">
+      <c r="L15" s="225">
         <f>'Page 1'!O15+'Page 2'!K15</f>
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="270" t="s">
+      <c r="A16" s="278" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="262" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="299"/>
+      <c r="D16" s="263"/>
       <c r="E16" s="78">
         <v>5</v>
       </c>
@@ -5421,20 +5471,20 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L16" s="230">
+      <c r="L16" s="226">
         <f>'Page 1'!O16+'Page 2'!K16</f>
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="271"/>
+      <c r="A17" s="279"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="264" t="s">
+      <c r="C17" s="275" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="265"/>
+      <c r="D17" s="276"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5457,20 +5507,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L17" s="231">
+      <c r="L17" s="227">
         <f>'Page 1'!O17+'Page 2'!K17</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="272"/>
+      <c r="A18" s="280"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="273" t="s">
+      <c r="C18" s="271" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="274"/>
+      <c r="D18" s="272"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5493,7 +5543,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="231">
+      <c r="L18" s="227">
         <f>'Page 1'!O18+'Page 2'!K18</f>
         <v>0</v>
       </c>
@@ -5505,10 +5555,10 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="275" t="s">
+      <c r="C19" s="239" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="259"/>
+      <c r="D19" s="238"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
         <v>1</v>
@@ -5523,7 +5573,7 @@
       </c>
       <c r="H19" s="76">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="76">
         <f t="shared" si="2"/>
@@ -5535,24 +5585,24 @@
       </c>
       <c r="K19" s="77">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L19" s="229">
+        <v>2</v>
+      </c>
+      <c r="L19" s="225">
         <f>'Page 1'!O19+'Page 2'!K19</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="270" t="s">
+      <c r="A20" s="278" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="298" t="s">
+      <c r="C20" s="262" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="299"/>
+      <c r="D20" s="263"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5563,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="79">
         <v>0</v>
@@ -5573,22 +5623,22 @@
       </c>
       <c r="K20" s="89">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="230">
+        <v>1</v>
+      </c>
+      <c r="L20" s="226">
         <f>'Page 1'!O20+'Page 2'!K20</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="271"/>
+      <c r="A21" s="279"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="269" t="s">
+      <c r="C21" s="277" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="265"/>
+      <c r="D21" s="276"/>
       <c r="E21" s="33">
         <v>1</v>
       </c>
@@ -5611,20 +5661,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="231">
+      <c r="L21" s="227">
         <f>'Page 1'!O21+'Page 2'!K21</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="271"/>
+      <c r="A22" s="279"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="264" t="s">
+      <c r="C22" s="275" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="265"/>
+      <c r="D22" s="276"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5647,20 +5697,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="231">
+      <c r="L22" s="227">
         <f>'Page 1'!O22+'Page 2'!K22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="272"/>
+      <c r="A23" s="280"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="273" t="s">
+      <c r="C23" s="271" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="274"/>
+      <c r="D23" s="272"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5683,7 +5733,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="231">
+      <c r="L23" s="227">
         <f>'Page 1'!O23+'Page 2'!K23</f>
         <v>0</v>
       </c>
@@ -5698,10 +5748,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="258" t="s">
+      <c r="C24" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="259"/>
+      <c r="D24" s="238"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
         <v>5</v>
@@ -5716,7 +5766,7 @@
       </c>
       <c r="H24" s="76">
         <f>SUM(H14+H15)-H19</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I24" s="76">
         <f>SUM(I14+I15)-I19</f>
@@ -5728,11 +5778,11 @@
       </c>
       <c r="K24" s="77">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="L24" s="229">
+        <v>13</v>
+      </c>
+      <c r="L24" s="225">
         <f>'Page 1'!O24+'Page 2'!K24</f>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5742,10 +5792,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="237" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="259"/>
+      <c r="D25" s="238"/>
       <c r="E25" s="40">
         <v>0</v>
       </c>
@@ -5924,21 +5974,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="L6:L12"/>
@@ -5955,6 +5990,21 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5971,7 +6021,7 @@
     <col min="2" max="2" width="45.7109375" style="122" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" style="123" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" style="123" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="123" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="123" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="122" customWidth="1"/>
     <col min="7" max="7" width="21.140625" style="122" customWidth="1"/>
   </cols>
@@ -5991,275 +6041,275 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="296" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="318"/>
-      <c r="C3" s="319"/>
-      <c r="D3" s="319"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="318"/>
-      <c r="G3" s="318"/>
+      <c r="B3" s="297"/>
+      <c r="C3" s="298"/>
+      <c r="D3" s="298"/>
+      <c r="E3" s="298"/>
+      <c r="F3" s="297"/>
+      <c r="G3" s="297"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="248"/>
-      <c r="B4" s="318"/>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="319"/>
-      <c r="F4" s="318"/>
-      <c r="G4" s="318"/>
+      <c r="A4" s="299"/>
+      <c r="B4" s="297"/>
+      <c r="C4" s="298"/>
+      <c r="D4" s="298"/>
+      <c r="E4" s="298"/>
+      <c r="F4" s="297"/>
+      <c r="G4" s="297"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="323" t="s">
+      <c r="A5" s="303" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="325" t="s">
+      <c r="B5" s="305" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="326" t="s">
+      <c r="C5" s="306" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="324" t="s">
+      <c r="D5" s="304" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="324" t="s">
+      <c r="E5" s="304" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="325" t="s">
+      <c r="F5" s="305" t="s">
         <v>101</v>
       </c>
-      <c r="G5" s="325" t="s">
+      <c r="G5" s="305" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="261"/>
-      <c r="B6" s="261"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
-      <c r="G6" s="261"/>
+      <c r="A6" s="241"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="241"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="261"/>
-      <c r="B7" s="261"/>
-      <c r="C7" s="261"/>
-      <c r="D7" s="261"/>
-      <c r="E7" s="261"/>
-      <c r="F7" s="261"/>
-      <c r="G7" s="261"/>
+      <c r="A7" s="241"/>
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="241"/>
+      <c r="E7" s="241"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="262"/>
-      <c r="B8" s="262"/>
-      <c r="C8" s="262"/>
-      <c r="D8" s="262"/>
-      <c r="E8" s="262"/>
-      <c r="F8" s="262"/>
-      <c r="G8" s="262"/>
+      <c r="A8" s="242"/>
+      <c r="B8" s="242"/>
+      <c r="C8" s="242"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="242"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="327" t="s">
+      <c r="A9" s="307" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="328"/>
-      <c r="C9" s="328"/>
-      <c r="D9" s="328"/>
-      <c r="E9" s="328"/>
-      <c r="F9" s="328"/>
-      <c r="G9" s="329"/>
-    </row>
-    <row r="10" spans="1:7" s="130" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="126"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-    </row>
-    <row r="11" spans="1:7" s="130" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="126"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="135"/>
-    </row>
-    <row r="12" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="131"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="135"/>
-    </row>
-    <row r="13" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="131"/>
-      <c r="B13" s="135"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="135"/>
-    </row>
-    <row r="14" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="133"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-    </row>
-    <row r="15" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="133"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-    </row>
-    <row r="16" spans="1:7" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="133"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="308"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="309"/>
+    </row>
+    <row r="10" spans="1:7" s="126" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="338">
+        <v>4671</v>
+      </c>
+      <c r="B10" s="339" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="340">
+        <v>45866</v>
+      </c>
+      <c r="D10" s="341">
+        <v>46142</v>
+      </c>
+      <c r="E10" s="341">
+        <v>46233</v>
+      </c>
+      <c r="F10" s="342" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="343" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="126" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="334"/>
+      <c r="B11" s="335"/>
+      <c r="C11" s="336"/>
+      <c r="D11" s="335"/>
+      <c r="E11" s="335"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="335"/>
+    </row>
+    <row r="12" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="127"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="131"/>
+    </row>
+    <row r="13" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="127"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="131"/>
+    </row>
+    <row r="14" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="129"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+    </row>
+    <row r="15" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="129"/>
+      <c r="B15" s="130"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+    </row>
+    <row r="16" spans="1:7" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="129"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="320" t="s">
+      <c r="A17" s="300" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="321"/>
-      <c r="C17" s="321"/>
-      <c r="D17" s="321"/>
-      <c r="E17" s="321"/>
-      <c r="F17" s="321"/>
-      <c r="G17" s="322"/>
-    </row>
-    <row r="18" spans="1:7" s="130" customFormat="1" ht="108" x14ac:dyDescent="0.2">
-      <c r="A18" s="234">
+      <c r="B17" s="301"/>
+      <c r="C17" s="301"/>
+      <c r="D17" s="301"/>
+      <c r="E17" s="301"/>
+      <c r="F17" s="301"/>
+      <c r="G17" s="302"/>
+    </row>
+    <row r="18" spans="1:7" s="126" customFormat="1" ht="108" x14ac:dyDescent="0.2">
+      <c r="A18" s="230">
         <v>744</v>
       </c>
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="231" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="237">
+      <c r="C18" s="233">
         <v>45215</v>
       </c>
-      <c r="D18" s="237">
+      <c r="D18" s="233">
         <v>46085</v>
       </c>
-      <c r="E18" s="238">
+      <c r="E18" s="234">
         <v>46179</v>
       </c>
-      <c r="F18" s="233" t="s">
+      <c r="F18" s="229" t="s">
+        <v>231</v>
+      </c>
+      <c r="G18" s="236" t="s">
         <v>232</v>
       </c>
-      <c r="G18" s="240" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="132" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A19" s="236">
+    </row>
+    <row r="19" spans="1:7" s="128" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A19" s="232">
         <v>754</v>
       </c>
-      <c r="B19" s="235" t="s">
+      <c r="B19" s="231" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="233">
         <v>45530</v>
       </c>
-      <c r="D19" s="237">
+      <c r="D19" s="233">
         <v>46085</v>
       </c>
-      <c r="E19" s="238">
+      <c r="E19" s="234">
         <v>46179</v>
       </c>
-      <c r="F19" s="233" t="s">
+      <c r="F19" s="229" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" s="236" t="s">
         <v>232</v>
       </c>
-      <c r="G19" s="240" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="132" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="236">
-        <v>755</v>
-      </c>
-      <c r="B20" s="235" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="239">
-        <v>45579</v>
-      </c>
-      <c r="D20" s="237">
-        <v>46057</v>
-      </c>
-      <c r="E20" s="238">
-        <v>46147</v>
-      </c>
-      <c r="F20" s="233" t="s">
-        <v>232</v>
-      </c>
-      <c r="G20" s="240" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="232"/>
-      <c r="B21" s="232"/>
-      <c r="C21" s="232"/>
-      <c r="D21" s="232"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="232"/>
-      <c r="G21" s="232"/>
-    </row>
-    <row r="22" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="133"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-    </row>
-    <row r="23" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="138"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-    </row>
-    <row r="24" spans="1:7" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="139"/>
-      <c r="B24" s="140"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
+    </row>
+    <row r="20" spans="1:7" s="128" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="232"/>
+      <c r="B20" s="231"/>
+      <c r="C20" s="235"/>
+      <c r="D20" s="233"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="229"/>
+      <c r="G20" s="236"/>
+    </row>
+    <row r="21" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="228"/>
+      <c r="B21" s="228"/>
+      <c r="C21" s="228"/>
+      <c r="D21" s="228"/>
+      <c r="E21" s="228"/>
+      <c r="F21" s="228"/>
+      <c r="G21" s="228"/>
+    </row>
+    <row r="22" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="129"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+    </row>
+    <row r="23" spans="1:7" s="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="129"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+    </row>
+    <row r="24" spans="1:7" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="135"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="144"/>
+      <c r="C25" s="140"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
+      <c r="B26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:G20">
@@ -6313,16 +6363,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="310" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="331"/>
-      <c r="F1" s="146" t="s">
+      <c r="B1" s="311"/>
+      <c r="C1" s="312"/>
+      <c r="F1" s="142" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
       <c r="S1" s="118" t="s">
         <v>108</v>
       </c>
@@ -6331,11 +6381,11 @@
       <c r="B2" s="120" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="148">
+      <c r="C2" s="144">
         <f>SUM(D3:D6)</f>
-        <v>10</v>
-      </c>
-      <c r="D2" s="149"/>
+        <v>11</v>
+      </c>
+      <c r="D2" s="145"/>
       <c r="G2" s="120" t="s">
         <v>110</v>
       </c>
@@ -6347,15 +6397,15 @@
       <c r="B3" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="150">
-        <v>3</v>
+      <c r="C3" s="145"/>
+      <c r="D3" s="146">
+        <v>2</v>
       </c>
       <c r="H3" s="120" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="151"/>
-      <c r="O3" s="152">
+      <c r="I3" s="147"/>
+      <c r="O3" s="148">
         <v>0</v>
       </c>
     </row>
@@ -6363,15 +6413,15 @@
       <c r="B4" s="120" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="149"/>
-      <c r="D4" s="153">
+      <c r="C4" s="145"/>
+      <c r="D4" s="149">
         <v>5</v>
       </c>
       <c r="H4" s="120" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="151"/>
-      <c r="O4" s="152">
+      <c r="I4" s="147"/>
+      <c r="O4" s="148">
         <v>0</v>
       </c>
     </row>
@@ -6379,24 +6429,24 @@
       <c r="B5" s="120" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="153">
-        <v>0</v>
+      <c r="C5" s="145"/>
+      <c r="D5" s="149">
+        <v>2</v>
       </c>
       <c r="H5" s="120" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="151"/>
-      <c r="O5" s="152">
+      <c r="I5" s="147"/>
+      <c r="O5" s="148">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="150" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="155"/>
-      <c r="D6" s="156">
+      <c r="C6" s="151"/>
+      <c r="D6" s="152">
         <v>2</v>
       </c>
     </row>
@@ -6404,10 +6454,10 @@
       <c r="B7" s="120" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="149"/>
-      <c r="D7" s="157">
+      <c r="C7" s="145"/>
+      <c r="D7" s="153">
         <f>SUM(C8:C13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>120</v>
@@ -6417,85 +6467,85 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="158" t="s">
+      <c r="B8" s="154" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="159">
-        <v>0</v>
-      </c>
-      <c r="D8" s="160"/>
+      <c r="C8" s="155">
+        <v>0</v>
+      </c>
+      <c r="D8" s="156"/>
       <c r="H8" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="I8" s="161"/>
-      <c r="O8" s="162">
+      <c r="I8" s="157"/>
+      <c r="O8" s="158">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="158" t="s">
+      <c r="B9" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="153">
-        <v>0</v>
-      </c>
-      <c r="D9" s="149"/>
+      <c r="C9" s="149">
+        <v>0</v>
+      </c>
+      <c r="D9" s="145"/>
       <c r="H9" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="I9" s="161"/>
-      <c r="O9" s="163">
+      <c r="I9" s="157"/>
+      <c r="O9" s="159">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="158" t="s">
+      <c r="B10" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="153">
-        <v>0</v>
-      </c>
-      <c r="D10" s="149"/>
+      <c r="C10" s="149">
+        <v>0</v>
+      </c>
+      <c r="D10" s="145"/>
       <c r="H10" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="I10" s="161"/>
-      <c r="O10" s="163">
+      <c r="I10" s="157"/>
+      <c r="O10" s="159">
         <v>2</v>
       </c>
-      <c r="R10" s="164"/>
+      <c r="R10" s="160"/>
     </row>
     <row r="11" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="158" t="s">
+      <c r="B11" s="154" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="153">
-        <v>0</v>
-      </c>
-      <c r="D11" s="149"/>
-      <c r="I11" s="161"/>
-      <c r="K11" s="161"/>
+      <c r="C11" s="149">
+        <v>1</v>
+      </c>
+      <c r="D11" s="145"/>
+      <c r="I11" s="157"/>
+      <c r="K11" s="157"/>
     </row>
     <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="158" t="s">
+      <c r="B12" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="153">
+      <c r="C12" s="149">
         <v>2</v>
       </c>
-      <c r="D12" s="149"/>
-      <c r="I12" s="161"/>
-      <c r="K12" s="161"/>
+      <c r="D12" s="145"/>
+      <c r="I12" s="157"/>
+      <c r="K12" s="157"/>
     </row>
     <row r="13" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="158" t="s">
+      <c r="B13" s="154" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="153">
+      <c r="C13" s="149">
         <v>0</v>
       </c>
       <c r="M13" s="118"/>
-      <c r="O13" s="165" t="s">
+      <c r="O13" s="161" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6506,24 +6556,24 @@
       <c r="H14" s="120" t="s">
         <v>133</v>
       </c>
-      <c r="M14" s="165" t="s">
+      <c r="M14" s="161" t="s">
         <v>134</v>
       </c>
-      <c r="O14" s="165" t="s">
+      <c r="O14" s="161" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="147" t="s">
+      <c r="A15" s="143" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="M15" s="162">
-        <v>0</v>
-      </c>
-      <c r="O15" s="162">
+      <c r="M15" s="158">
+        <v>0</v>
+      </c>
+      <c r="O15" s="158">
         <v>0</v>
       </c>
     </row>
@@ -6531,17 +6581,17 @@
       <c r="B16" s="120" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="149"/>
-      <c r="D16" s="150">
+      <c r="C16" s="145"/>
+      <c r="D16" s="146">
         <v>0</v>
       </c>
       <c r="H16" s="120" t="s">
         <v>139</v>
       </c>
-      <c r="M16" s="163">
-        <v>0</v>
-      </c>
-      <c r="O16" s="163">
+      <c r="M16" s="159">
+        <v>0</v>
+      </c>
+      <c r="O16" s="159">
         <v>0</v>
       </c>
     </row>
@@ -6549,48 +6599,48 @@
       <c r="B17" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="149"/>
-      <c r="D17" s="150">
+      <c r="C17" s="145"/>
+      <c r="D17" s="146">
         <v>3</v>
       </c>
-      <c r="I17" s="161"/>
-      <c r="K17" s="161"/>
+      <c r="I17" s="157"/>
+      <c r="K17" s="157"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="144" t="s">
+      <c r="B18" s="140" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="166"/>
-      <c r="D18" s="167">
+      <c r="C18" s="162"/>
+      <c r="D18" s="163">
         <f>SUM(C19:C20)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="161"/>
-      <c r="K18" s="161"/>
+      <c r="I18" s="157"/>
+      <c r="K18" s="157"/>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="120" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="150">
-        <v>0</v>
-      </c>
-      <c r="D19" s="149"/>
+      <c r="C19" s="146">
+        <v>0</v>
+      </c>
+      <c r="D19" s="145"/>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="120" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="153">
-        <v>0</v>
-      </c>
-      <c r="D20" s="149"/>
-      <c r="F20" s="330" t="s">
+      <c r="C20" s="149">
+        <v>0</v>
+      </c>
+      <c r="D20" s="145"/>
+      <c r="F20" s="310" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="242"/>
-      <c r="H20" s="242"/>
-      <c r="K20" s="165" t="s">
+      <c r="G20" s="311"/>
+      <c r="H20" s="311"/>
+      <c r="K20" s="161" t="s">
         <v>145</v>
       </c>
       <c r="M20" s="120" t="s">
@@ -6602,7 +6652,7 @@
       <c r="Q20" s="118" t="s">
         <v>147</v>
       </c>
-      <c r="S20" s="168" t="s">
+      <c r="S20" s="164" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6610,15 +6660,15 @@
       <c r="B21" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="149"/>
-      <c r="D21" s="167">
+      <c r="C21" s="145"/>
+      <c r="D21" s="163">
         <f>SUM(D16:D17)-D18</f>
         <v>3</v>
       </c>
-      <c r="I21" s="165" t="s">
+      <c r="I21" s="161" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="165" t="s">
+      <c r="K21" s="161" t="s">
         <v>151</v>
       </c>
       <c r="M21" s="120" t="s">
@@ -6627,116 +6677,116 @@
       <c r="O21" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="Q21" s="165" t="s">
+      <c r="Q21" s="161" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
       <c r="G22" s="120" t="s">
         <v>110</v>
       </c>
       <c r="H22" s="120" t="s">
         <v>154</v>
       </c>
-      <c r="I22" s="169">
+      <c r="I22" s="165">
         <v>21</v>
       </c>
       <c r="J22" s="124"/>
-      <c r="K22" s="169">
+      <c r="K22" s="165">
         <v>10</v>
       </c>
       <c r="L22" s="124"/>
-      <c r="M22" s="169">
+      <c r="M22" s="165">
         <v>0</v>
       </c>
       <c r="N22" s="124"/>
-      <c r="O22" s="169">
+      <c r="O22" s="165">
         <v>0</v>
       </c>
       <c r="P22" s="124"/>
-      <c r="Q22" s="169">
+      <c r="Q22" s="165">
         <v>0</v>
       </c>
       <c r="R22" s="124"/>
-      <c r="S22" s="170">
+      <c r="S22" s="166">
         <f t="shared" ref="S22:S32" si="0">SUM(I22+K22+M22+O22+Q22)</f>
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="147" t="s">
+      <c r="A23" s="143" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
       <c r="G23" s="120" t="s">
         <v>120</v>
       </c>
       <c r="H23" s="120" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="171">
+      <c r="I23" s="167">
         <v>0</v>
       </c>
       <c r="J23" s="124"/>
-      <c r="K23" s="171">
-        <v>3</v>
+      <c r="K23" s="167">
+        <v>2</v>
       </c>
       <c r="L23" s="124"/>
-      <c r="M23" s="171">
+      <c r="M23" s="167">
         <v>0</v>
       </c>
       <c r="N23" s="124"/>
-      <c r="O23" s="171">
+      <c r="O23" s="167">
         <v>0</v>
       </c>
       <c r="P23" s="124"/>
-      <c r="Q23" s="171">
+      <c r="Q23" s="167">
         <v>0</v>
       </c>
       <c r="R23" s="124"/>
-      <c r="S23" s="170">
+      <c r="S23" s="166">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="162">
-        <v>0</v>
-      </c>
-      <c r="D24" s="149"/>
+      <c r="C24" s="158">
+        <v>0</v>
+      </c>
+      <c r="D24" s="145"/>
       <c r="G24" s="120" t="s">
         <v>132</v>
       </c>
       <c r="H24" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="I24" s="171">
+      <c r="I24" s="167">
         <v>0</v>
       </c>
       <c r="J24" s="124"/>
-      <c r="K24" s="171">
+      <c r="K24" s="167">
         <v>1</v>
       </c>
       <c r="L24" s="124"/>
-      <c r="M24" s="171">
+      <c r="M24" s="167">
         <v>0</v>
       </c>
       <c r="N24" s="124"/>
-      <c r="O24" s="171">
+      <c r="O24" s="167">
         <v>0</v>
       </c>
       <c r="P24" s="124"/>
-      <c r="Q24" s="171">
+      <c r="Q24" s="167">
         <v>0</v>
       </c>
       <c r="R24" s="124"/>
-      <c r="S24" s="170">
+      <c r="S24" s="166">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6745,37 +6795,37 @@
       <c r="B25" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="163">
+      <c r="C25" s="159">
         <v>1</v>
       </c>
-      <c r="D25" s="149"/>
+      <c r="D25" s="145"/>
       <c r="G25" s="120" t="s">
         <v>160</v>
       </c>
       <c r="H25" s="120" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="171">
+      <c r="I25" s="167">
         <v>0</v>
       </c>
       <c r="J25" s="124"/>
-      <c r="K25" s="171">
+      <c r="K25" s="167">
         <v>0</v>
       </c>
       <c r="L25" s="124"/>
-      <c r="M25" s="171">
+      <c r="M25" s="167">
         <v>0</v>
       </c>
       <c r="N25" s="124"/>
-      <c r="O25" s="171">
+      <c r="O25" s="167">
         <v>0</v>
       </c>
       <c r="P25" s="124"/>
-      <c r="Q25" s="171">
+      <c r="Q25" s="167">
         <v>0</v>
       </c>
       <c r="R25" s="124"/>
-      <c r="S25" s="170">
+      <c r="S25" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6784,37 +6834,37 @@
       <c r="B26" s="120" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="163">
+      <c r="C26" s="159">
         <v>1</v>
       </c>
-      <c r="D26" s="149"/>
+      <c r="D26" s="145"/>
       <c r="G26" s="120" t="s">
         <v>163</v>
       </c>
       <c r="H26" s="120" t="s">
         <v>164</v>
       </c>
-      <c r="I26" s="171">
+      <c r="I26" s="167">
         <v>0</v>
       </c>
       <c r="J26" s="124"/>
-      <c r="K26" s="171">
+      <c r="K26" s="167">
         <v>0</v>
       </c>
       <c r="L26" s="124"/>
-      <c r="M26" s="171">
+      <c r="M26" s="167">
         <v>0</v>
       </c>
       <c r="N26" s="124"/>
-      <c r="O26" s="171">
+      <c r="O26" s="167">
         <v>0</v>
       </c>
       <c r="P26" s="124"/>
-      <c r="Q26" s="171">
+      <c r="Q26" s="167">
         <v>0</v>
       </c>
       <c r="R26" s="124"/>
-      <c r="S26" s="170">
+      <c r="S26" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6823,37 +6873,37 @@
       <c r="B27" s="120" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="163">
-        <v>0</v>
-      </c>
-      <c r="D27" s="149"/>
+      <c r="C27" s="159">
+        <v>0</v>
+      </c>
+      <c r="D27" s="145"/>
       <c r="G27" s="120" t="s">
         <v>166</v>
       </c>
       <c r="H27" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="I27" s="171">
+      <c r="I27" s="167">
         <v>0</v>
       </c>
       <c r="J27" s="124"/>
-      <c r="K27" s="171">
+      <c r="K27" s="167">
         <v>0</v>
       </c>
       <c r="L27" s="124"/>
-      <c r="M27" s="171">
+      <c r="M27" s="167">
         <v>0</v>
       </c>
       <c r="N27" s="124"/>
-      <c r="O27" s="171">
+      <c r="O27" s="167">
         <v>0</v>
       </c>
       <c r="P27" s="124"/>
-      <c r="Q27" s="171">
+      <c r="Q27" s="167">
         <v>0</v>
       </c>
       <c r="R27" s="124"/>
-      <c r="S27" s="170">
+      <c r="S27" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6862,38 +6912,38 @@
       <c r="B28" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="157">
+      <c r="C28" s="153">
         <f>SUM(C24:C25)-SUM(C26:C27)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="149"/>
+      <c r="D28" s="145"/>
       <c r="G28" s="120" t="s">
         <v>169</v>
       </c>
       <c r="H28" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="I28" s="171">
+      <c r="I28" s="167">
         <v>0</v>
       </c>
       <c r="J28" s="124"/>
-      <c r="K28" s="171">
+      <c r="K28" s="167">
         <v>0</v>
       </c>
       <c r="L28" s="124"/>
-      <c r="M28" s="171">
+      <c r="M28" s="167">
         <v>0</v>
       </c>
       <c r="N28" s="124"/>
-      <c r="O28" s="171">
+      <c r="O28" s="167">
         <v>0</v>
       </c>
       <c r="P28" s="124"/>
-      <c r="Q28" s="171">
+      <c r="Q28" s="167">
         <v>0</v>
       </c>
       <c r="R28" s="124"/>
-      <c r="S28" s="170">
+      <c r="S28" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6902,35 +6952,35 @@
       <c r="B29" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="160"/>
-      <c r="D29" s="149"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="145"/>
       <c r="G29" s="120" t="s">
         <v>172</v>
       </c>
       <c r="H29" s="120" t="s">
         <v>173</v>
       </c>
-      <c r="I29" s="171">
+      <c r="I29" s="167">
         <v>0</v>
       </c>
       <c r="J29" s="124"/>
-      <c r="K29" s="171">
+      <c r="K29" s="167">
         <v>0</v>
       </c>
       <c r="L29" s="124"/>
-      <c r="M29" s="171">
+      <c r="M29" s="167">
         <v>0</v>
       </c>
       <c r="N29" s="124"/>
-      <c r="O29" s="171">
+      <c r="O29" s="167">
         <v>0</v>
       </c>
       <c r="P29" s="124"/>
-      <c r="Q29" s="171">
+      <c r="Q29" s="167">
         <v>0</v>
       </c>
       <c r="R29" s="124"/>
-      <c r="S29" s="170">
+      <c r="S29" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6939,37 +6989,37 @@
       <c r="B30" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="152">
-        <v>0</v>
-      </c>
-      <c r="D30" s="149"/>
+      <c r="C30" s="148">
+        <v>0</v>
+      </c>
+      <c r="D30" s="145"/>
       <c r="G30" s="120" t="s">
         <v>175</v>
       </c>
       <c r="H30" s="120" t="s">
         <v>176</v>
       </c>
-      <c r="I30" s="171">
+      <c r="I30" s="167">
         <v>0</v>
       </c>
       <c r="J30" s="124"/>
-      <c r="K30" s="171">
+      <c r="K30" s="167">
         <v>0</v>
       </c>
       <c r="L30" s="124"/>
-      <c r="M30" s="171">
+      <c r="M30" s="167">
         <v>0</v>
       </c>
       <c r="N30" s="124"/>
-      <c r="O30" s="171">
+      <c r="O30" s="167">
         <v>0</v>
       </c>
       <c r="P30" s="124"/>
-      <c r="Q30" s="171">
+      <c r="Q30" s="167">
         <v>0</v>
       </c>
       <c r="R30" s="124"/>
-      <c r="S30" s="170">
+      <c r="S30" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6978,195 +7028,195 @@
       <c r="B31" s="120" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="172">
+      <c r="C31" s="168">
         <v>2</v>
       </c>
-      <c r="D31" s="149"/>
+      <c r="D31" s="145"/>
       <c r="G31" s="120" t="s">
         <v>178</v>
       </c>
       <c r="H31" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="171">
+      <c r="I31" s="167">
         <v>0</v>
       </c>
       <c r="J31" s="124"/>
-      <c r="K31" s="171">
+      <c r="K31" s="167">
         <v>0</v>
       </c>
       <c r="L31" s="124"/>
-      <c r="M31" s="171">
+      <c r="M31" s="167">
         <v>0</v>
       </c>
       <c r="N31" s="124"/>
-      <c r="O31" s="171">
+      <c r="O31" s="167">
         <v>0</v>
       </c>
       <c r="P31" s="124"/>
-      <c r="Q31" s="171">
+      <c r="Q31" s="167">
         <v>0</v>
       </c>
       <c r="R31" s="124"/>
-      <c r="S31" s="170">
+      <c r="S31" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="144"/>
+      <c r="D32" s="140"/>
       <c r="G32" s="120" t="s">
         <v>180</v>
       </c>
       <c r="H32" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="171">
+      <c r="I32" s="167">
         <v>0</v>
       </c>
       <c r="J32" s="124"/>
-      <c r="K32" s="171">
+      <c r="K32" s="167">
         <v>0</v>
       </c>
       <c r="L32" s="124"/>
-      <c r="M32" s="171">
+      <c r="M32" s="167">
         <v>0</v>
       </c>
       <c r="N32" s="124"/>
-      <c r="O32" s="171">
+      <c r="O32" s="167">
         <v>0</v>
       </c>
       <c r="P32" s="124"/>
-      <c r="Q32" s="171">
+      <c r="Q32" s="167">
         <v>0</v>
       </c>
       <c r="R32" s="124"/>
-      <c r="S32" s="170">
+      <c r="S32" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="144"/>
-      <c r="H33" s="147" t="s">
+      <c r="D33" s="140"/>
+      <c r="H33" s="143" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="170">
+      <c r="I33" s="166">
         <f>SUM(I22:I32)</f>
         <v>21</v>
       </c>
-      <c r="J33" s="173"/>
-      <c r="K33" s="170">
+      <c r="J33" s="169"/>
+      <c r="K33" s="166">
         <f>SUM(K22:K32)</f>
-        <v>14</v>
-      </c>
-      <c r="L33" s="174"/>
-      <c r="M33" s="170">
+        <v>13</v>
+      </c>
+      <c r="L33" s="170"/>
+      <c r="M33" s="166">
         <f>SUM(M22:M32)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="174"/>
-      <c r="O33" s="170">
+      <c r="N33" s="170"/>
+      <c r="O33" s="166">
         <f>SUM(O22:O32)</f>
         <v>0</v>
       </c>
-      <c r="P33" s="174"/>
-      <c r="Q33" s="170">
+      <c r="P33" s="170"/>
+      <c r="Q33" s="166">
         <f>SUM(Q22:Q32)</f>
         <v>0</v>
       </c>
-      <c r="S33" s="170">
+      <c r="S33" s="166">
         <f>SUM(S22:S32)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="175"/>
-      <c r="B34" s="175"/>
-      <c r="D34" s="144"/>
-      <c r="I34" s="176"/>
-      <c r="J34" s="177"/>
-      <c r="K34" s="176"/>
-      <c r="L34" s="177"/>
+      <c r="A34" s="171"/>
+      <c r="B34" s="171"/>
+      <c r="D34" s="140"/>
+      <c r="I34" s="172"/>
+      <c r="J34" s="173"/>
+      <c r="K34" s="172"/>
+      <c r="L34" s="173"/>
       <c r="M34" s="124"/>
-      <c r="N34" s="177"/>
+      <c r="N34" s="173"/>
       <c r="O34" s="124"/>
-      <c r="P34" s="177"/>
-      <c r="Q34" s="176"/>
-      <c r="R34" s="174"/>
-      <c r="S34" s="178"/>
+      <c r="P34" s="173"/>
+      <c r="Q34" s="172"/>
+      <c r="R34" s="170"/>
+      <c r="S34" s="174"/>
     </row>
     <row r="35" spans="1:19" s="120" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="144" t="s">
+      <c r="A35" s="140" t="s">
         <v>183</v>
       </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="G35" s="147"/>
+      <c r="B35" s="140"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="140"/>
+      <c r="G35" s="143"/>
       <c r="I35" s="118"/>
       <c r="K35" s="118"/>
       <c r="Q35" s="118"/>
       <c r="S35" s="118"/>
     </row>
     <row r="36" spans="1:19" s="120" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="140" t="s">
         <v>184</v>
       </c>
-      <c r="B36" s="144"/>
-      <c r="C36" s="144"/>
-      <c r="D36" s="144"/>
+      <c r="B36" s="140"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="140"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="144"/>
-      <c r="F37" s="144"/>
-      <c r="G37" s="144"/>
-      <c r="H37" s="144"/>
-      <c r="I37" s="144"/>
-      <c r="J37" s="144"/>
-      <c r="K37" s="144"/>
-      <c r="L37" s="144"/>
-      <c r="M37" s="144"/>
-      <c r="N37" s="144"/>
-      <c r="O37" s="144"/>
-      <c r="P37" s="144"/>
-      <c r="Q37" s="144"/>
-      <c r="R37" s="144"/>
-      <c r="S37" s="144"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
+      <c r="M37" s="140"/>
+      <c r="N37" s="140"/>
+      <c r="O37" s="140"/>
+      <c r="P37" s="140"/>
+      <c r="Q37" s="140"/>
+      <c r="R37" s="140"/>
+      <c r="S37" s="140"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="144"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="144"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="144"/>
-      <c r="J38" s="144"/>
-      <c r="K38" s="144"/>
-      <c r="L38" s="144"/>
-      <c r="M38" s="144"/>
-      <c r="N38" s="144"/>
-      <c r="O38" s="144"/>
-      <c r="P38" s="144"/>
-      <c r="Q38" s="144"/>
-      <c r="R38" s="144"/>
-      <c r="S38" s="144"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="140"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="140"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="140"/>
+      <c r="M38" s="140"/>
+      <c r="N38" s="140"/>
+      <c r="O38" s="140"/>
+      <c r="P38" s="140"/>
+      <c r="Q38" s="140"/>
+      <c r="R38" s="140"/>
+      <c r="S38" s="140"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="144"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="144"/>
-      <c r="J39" s="144"/>
-      <c r="K39" s="144"/>
-      <c r="L39" s="144"/>
-      <c r="M39" s="144"/>
-      <c r="N39" s="144"/>
-      <c r="O39" s="144"/>
-      <c r="P39" s="144"/>
-      <c r="Q39" s="144"/>
-      <c r="R39" s="144"/>
-      <c r="S39" s="144"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="140"/>
+      <c r="N39" s="140"/>
+      <c r="O39" s="140"/>
+      <c r="P39" s="140"/>
+      <c r="Q39" s="140"/>
+      <c r="R39" s="140"/>
+      <c r="S39" s="140"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
@@ -7212,337 +7262,337 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="320" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
-      <c r="M1" s="242"/>
-      <c r="N1" s="242"/>
-      <c r="O1" s="242"/>
-      <c r="P1" s="242"/>
-      <c r="Q1" s="242"/>
-      <c r="R1" s="242"/>
-      <c r="S1" s="242"/>
-      <c r="T1" s="242"/>
-      <c r="U1" s="242"/>
-      <c r="V1" s="242"/>
-      <c r="W1" s="242"/>
-      <c r="X1" s="242"/>
-      <c r="Y1" s="242"/>
-      <c r="Z1" s="242"/>
-      <c r="AA1" s="242"/>
+      <c r="B1" s="311"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="311"/>
+      <c r="J1" s="311"/>
+      <c r="K1" s="311"/>
+      <c r="L1" s="311"/>
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="143" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="N2" s="179"/>
-      <c r="P2" s="147" t="s">
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="N2" s="175"/>
+      <c r="P2" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="147"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
-      <c r="Y2" s="147"/>
-      <c r="Z2" s="147"/>
-      <c r="AA2" s="147"/>
+      <c r="Q2" s="143"/>
+      <c r="R2" s="143"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="143"/>
+      <c r="AA2" s="143"/>
     </row>
     <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="143" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="N3" s="179"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="N3" s="175"/>
       <c r="Q3" s="120" t="s">
         <v>110</v>
       </c>
       <c r="R3" s="120" t="s">
         <v>189</v>
       </c>
-      <c r="Z3" s="180">
+      <c r="Z3" s="176">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="164"/>
-      <c r="M4" s="164"/>
-      <c r="N4" s="181"/>
-      <c r="W4" s="161"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="160"/>
+      <c r="N4" s="177"/>
+      <c r="W4" s="157"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="256" t="s">
+      <c r="C5" s="313" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="181"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="311"/>
+      <c r="G5" s="311"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="160"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="177"/>
       <c r="Q5" s="120" t="s">
         <v>120</v>
       </c>
       <c r="R5" s="120" t="s">
         <v>191</v>
       </c>
-      <c r="X5" s="182"/>
-      <c r="Y5" s="182"/>
-      <c r="Z5" s="182"/>
+      <c r="X5" s="178"/>
+      <c r="Y5" s="178"/>
+      <c r="Z5" s="178"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="256" t="s">
+      <c r="C6" s="313" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="242"/>
-      <c r="E6" s="242"/>
-      <c r="F6" s="242"/>
-      <c r="G6" s="242"/>
-      <c r="H6" s="180">
-        <v>0</v>
-      </c>
-      <c r="N6" s="179"/>
-      <c r="R6" s="257" t="s">
+      <c r="D6" s="311"/>
+      <c r="E6" s="311"/>
+      <c r="F6" s="311"/>
+      <c r="G6" s="311"/>
+      <c r="H6" s="176">
+        <v>0</v>
+      </c>
+      <c r="N6" s="175"/>
+      <c r="R6" s="318" t="s">
         <v>193</v>
       </c>
-      <c r="S6" s="251"/>
-      <c r="T6" s="251"/>
-      <c r="U6" s="251"/>
-      <c r="V6" s="251"/>
-      <c r="W6" s="251"/>
-      <c r="X6" s="251"/>
-      <c r="Y6" s="251"/>
-      <c r="Z6" s="251"/>
-      <c r="AA6" s="183"/>
+      <c r="S6" s="319"/>
+      <c r="T6" s="319"/>
+      <c r="U6" s="319"/>
+      <c r="V6" s="319"/>
+      <c r="W6" s="319"/>
+      <c r="X6" s="319"/>
+      <c r="Y6" s="319"/>
+      <c r="Z6" s="319"/>
+      <c r="AA6" s="179"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="256" t="s">
+      <c r="C7" s="313" t="s">
         <v>194</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="184">
-        <v>0</v>
-      </c>
-      <c r="N7" s="179"/>
-      <c r="R7" s="251"/>
-      <c r="S7" s="251"/>
-      <c r="T7" s="251"/>
-      <c r="U7" s="251"/>
-      <c r="V7" s="251"/>
-      <c r="W7" s="251"/>
-      <c r="X7" s="251"/>
-      <c r="Y7" s="251"/>
-      <c r="Z7" s="251"/>
-      <c r="AA7" s="183"/>
+      <c r="D7" s="311"/>
+      <c r="E7" s="311"/>
+      <c r="F7" s="311"/>
+      <c r="G7" s="311"/>
+      <c r="H7" s="180">
+        <v>0</v>
+      </c>
+      <c r="N7" s="175"/>
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
+      <c r="T7" s="319"/>
+      <c r="U7" s="319"/>
+      <c r="V7" s="319"/>
+      <c r="W7" s="319"/>
+      <c r="X7" s="319"/>
+      <c r="Y7" s="319"/>
+      <c r="Z7" s="319"/>
+      <c r="AA7" s="179"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="185">
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="181">
         <f>SUM(H6:H7)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="179"/>
-      <c r="R8" s="251"/>
-      <c r="S8" s="251"/>
-      <c r="T8" s="251"/>
-      <c r="U8" s="251"/>
-      <c r="V8" s="251"/>
-      <c r="W8" s="251"/>
-      <c r="X8" s="251"/>
-      <c r="Y8" s="251"/>
-      <c r="Z8" s="251"/>
-      <c r="AA8" s="183"/>
+      <c r="N8" s="175"/>
+      <c r="R8" s="319"/>
+      <c r="S8" s="319"/>
+      <c r="T8" s="319"/>
+      <c r="U8" s="319"/>
+      <c r="V8" s="319"/>
+      <c r="W8" s="319"/>
+      <c r="X8" s="319"/>
+      <c r="Y8" s="319"/>
+      <c r="Z8" s="319"/>
+      <c r="AA8" s="179"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H9" s="186" t="s">
+      <c r="H9" s="182" t="s">
         <v>195</v>
       </c>
-      <c r="J9" s="187" t="s">
+      <c r="J9" s="183" t="s">
         <v>196</v>
       </c>
-      <c r="K9" s="187"/>
-      <c r="L9" s="187" t="s">
+      <c r="K9" s="183"/>
+      <c r="L9" s="183" t="s">
         <v>197</v>
       </c>
-      <c r="N9" s="179"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="247"/>
-      <c r="W9" s="247"/>
-      <c r="X9" s="247"/>
-      <c r="Y9" s="247"/>
-      <c r="Z9" s="247"/>
-      <c r="AA9" s="147"/>
+      <c r="N9" s="175"/>
+      <c r="R9" s="317"/>
+      <c r="S9" s="317"/>
+      <c r="T9" s="317"/>
+      <c r="U9" s="317"/>
+      <c r="V9" s="317"/>
+      <c r="W9" s="317"/>
+      <c r="X9" s="317"/>
+      <c r="Y9" s="317"/>
+      <c r="Z9" s="317"/>
+      <c r="AA9" s="143"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="H10" s="180">
-        <v>0</v>
-      </c>
-      <c r="I10" s="164"/>
-      <c r="J10" s="180">
-        <v>0</v>
-      </c>
-      <c r="K10" s="188"/>
-      <c r="L10" s="180">
-        <v>0</v>
-      </c>
-      <c r="N10" s="179"/>
-      <c r="X10" s="147"/>
-      <c r="Y10" s="147"/>
-      <c r="Z10" s="189"/>
+      <c r="H10" s="176">
+        <v>0</v>
+      </c>
+      <c r="I10" s="160"/>
+      <c r="J10" s="176">
+        <v>0</v>
+      </c>
+      <c r="K10" s="184"/>
+      <c r="L10" s="176">
+        <v>0</v>
+      </c>
+      <c r="N10" s="175"/>
+      <c r="X10" s="143"/>
+      <c r="Y10" s="143"/>
+      <c r="Z10" s="185"/>
     </row>
     <row r="11" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M11" s="164"/>
-      <c r="N11" s="181"/>
-      <c r="P11" s="147" t="s">
+      <c r="M11" s="160"/>
+      <c r="N11" s="177"/>
+      <c r="P11" s="143" t="s">
         <v>199</v>
       </c>
-      <c r="W11" s="147"/>
-      <c r="Z11" s="180">
+      <c r="W11" s="143"/>
+      <c r="Z11" s="176">
         <v>8</v>
       </c>
-      <c r="AA11" s="190"/>
+      <c r="AA11" s="186"/>
     </row>
     <row r="12" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H12" s="164"/>
-      <c r="M12" s="164"/>
-      <c r="N12" s="181"/>
-      <c r="Q12" s="147"/>
-      <c r="R12" s="147"/>
-      <c r="S12" s="147"/>
-      <c r="T12" s="147"/>
-      <c r="U12" s="147"/>
-      <c r="V12" s="147"/>
-      <c r="W12" s="161"/>
-      <c r="AA12" s="190"/>
+      <c r="H12" s="160"/>
+      <c r="M12" s="160"/>
+      <c r="N12" s="177"/>
+      <c r="Q12" s="143"/>
+      <c r="R12" s="143"/>
+      <c r="S12" s="143"/>
+      <c r="T12" s="143"/>
+      <c r="U12" s="143"/>
+      <c r="V12" s="143"/>
+      <c r="W12" s="157"/>
+      <c r="AA12" s="186"/>
     </row>
     <row r="13" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="140" t="s">
         <v>200</v>
       </c>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="164"/>
-      <c r="N13" s="179"/>
-      <c r="P13" s="147" t="s">
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="160"/>
+      <c r="N13" s="175"/>
+      <c r="P13" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="W13" s="161"/>
+      <c r="W13" s="157"/>
       <c r="Z13" s="11"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="140" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="N14" s="179"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="N14" s="175"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="256" t="s">
+      <c r="C15" s="313" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="E15" s="242"/>
-      <c r="F15" s="242"/>
-      <c r="G15" s="242"/>
-      <c r="H15" s="180">
-        <v>0</v>
-      </c>
-      <c r="N15" s="179"/>
+      <c r="D15" s="311"/>
+      <c r="E15" s="311"/>
+      <c r="F15" s="311"/>
+      <c r="G15" s="311"/>
+      <c r="H15" s="176">
+        <v>0</v>
+      </c>
+      <c r="N15" s="175"/>
       <c r="Q15" s="120" t="s">
         <v>203</v>
       </c>
-      <c r="Z15" s="180">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="147"/>
+      <c r="Z15" s="176">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="143"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="256" t="s">
+      <c r="C16" s="313" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="184">
-        <v>0</v>
-      </c>
-      <c r="N16" s="179"/>
+      <c r="D16" s="311"/>
+      <c r="E16" s="311"/>
+      <c r="F16" s="311"/>
+      <c r="G16" s="311"/>
+      <c r="H16" s="180">
+        <v>0</v>
+      </c>
+      <c r="N16" s="175"/>
       <c r="Q16" s="120" t="s">
         <v>204</v>
       </c>
-      <c r="Z16" s="184">
+      <c r="Z16" s="180">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H17" s="185">
+      <c r="H17" s="181">
         <f>SUM(H15:H16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="179"/>
+      <c r="N17" s="175"/>
       <c r="Q17" s="120" t="s">
         <v>205</v>
       </c>
-      <c r="Z17" s="184">
+      <c r="Z17" s="180">
         <v>0</v>
       </c>
     </row>
@@ -7550,18 +7600,18 @@
       <c r="C18" s="120" t="s">
         <v>206</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="H18" s="164" t="s">
+      <c r="F18" s="160"/>
+      <c r="H18" s="160" t="s">
         <v>207</v>
       </c>
-      <c r="J18" s="164" t="s">
+      <c r="J18" s="160" t="s">
         <v>208</v>
       </c>
-      <c r="N18" s="179"/>
+      <c r="N18" s="175"/>
       <c r="Q18" s="120" t="s">
         <v>209</v>
       </c>
-      <c r="Z18" s="184">
+      <c r="Z18" s="180">
         <v>0</v>
       </c>
     </row>
@@ -7569,444 +7619,438 @@
       <c r="C19" s="120" t="s">
         <v>210</v>
       </c>
-      <c r="F19" s="161"/>
-      <c r="H19" s="180">
-        <v>0</v>
-      </c>
-      <c r="I19" s="164"/>
-      <c r="J19" s="180">
-        <v>0</v>
-      </c>
-      <c r="K19" s="164"/>
-      <c r="N19" s="179"/>
-      <c r="P19" s="191"/>
-      <c r="Q19" s="144"/>
-      <c r="R19" s="144"/>
-      <c r="S19" s="144"/>
-      <c r="T19" s="144"/>
-      <c r="U19" s="144"/>
-      <c r="V19" s="144"/>
-      <c r="W19" s="191"/>
-      <c r="X19" s="144"/>
-      <c r="Y19" s="144"/>
-      <c r="Z19" s="166"/>
+      <c r="F19" s="157"/>
+      <c r="H19" s="176">
+        <v>0</v>
+      </c>
+      <c r="I19" s="160"/>
+      <c r="J19" s="176">
+        <v>0</v>
+      </c>
+      <c r="K19" s="160"/>
+      <c r="N19" s="175"/>
+      <c r="P19" s="187"/>
+      <c r="Q19" s="140"/>
+      <c r="R19" s="140"/>
+      <c r="S19" s="140"/>
+      <c r="T19" s="140"/>
+      <c r="U19" s="140"/>
+      <c r="V19" s="140"/>
+      <c r="W19" s="187"/>
+      <c r="X19" s="140"/>
+      <c r="Y19" s="140"/>
+      <c r="Z19" s="162"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="N20" s="179"/>
-      <c r="Q20" s="191"/>
-      <c r="R20" s="191"/>
-      <c r="S20" s="191"/>
-      <c r="T20" s="191"/>
-      <c r="U20" s="191"/>
-      <c r="V20" s="191"/>
-      <c r="X20" s="191"/>
-      <c r="Y20" s="191"/>
-      <c r="Z20" s="191"/>
+      <c r="N20" s="175"/>
+      <c r="Q20" s="187"/>
+      <c r="R20" s="187"/>
+      <c r="S20" s="187"/>
+      <c r="T20" s="187"/>
+      <c r="U20" s="187"/>
+      <c r="V20" s="187"/>
+      <c r="X20" s="187"/>
+      <c r="Y20" s="187"/>
+      <c r="Z20" s="187"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="N21" s="179"/>
+      <c r="N21" s="175"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="252" t="s">
+      <c r="A23" s="326" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="242"/>
-      <c r="C23" s="242"/>
-      <c r="D23" s="242"/>
-      <c r="E23" s="242"/>
-      <c r="F23" s="242"/>
-      <c r="G23" s="242"/>
-      <c r="H23" s="242"/>
-      <c r="I23" s="242"/>
-      <c r="J23" s="242"/>
-      <c r="K23" s="242"/>
-      <c r="L23" s="242"/>
-      <c r="M23" s="242"/>
-      <c r="N23" s="242"/>
-      <c r="O23" s="242"/>
-      <c r="P23" s="242"/>
-      <c r="Q23" s="242"/>
-      <c r="R23" s="242"/>
-      <c r="S23" s="242"/>
-      <c r="T23" s="242"/>
-      <c r="U23" s="242"/>
-      <c r="V23" s="242"/>
-      <c r="W23" s="242"/>
-      <c r="X23" s="242"/>
-      <c r="Y23" s="242"/>
-      <c r="Z23" s="242"/>
-      <c r="AA23" s="242"/>
+      <c r="B23" s="311"/>
+      <c r="C23" s="311"/>
+      <c r="D23" s="311"/>
+      <c r="E23" s="311"/>
+      <c r="F23" s="311"/>
+      <c r="G23" s="311"/>
+      <c r="H23" s="311"/>
+      <c r="I23" s="311"/>
+      <c r="J23" s="311"/>
+      <c r="K23" s="311"/>
+      <c r="L23" s="311"/>
+      <c r="M23" s="311"/>
+      <c r="N23" s="311"/>
+      <c r="O23" s="311"/>
+      <c r="P23" s="311"/>
+      <c r="Q23" s="311"/>
+      <c r="R23" s="311"/>
+      <c r="S23" s="311"/>
+      <c r="T23" s="311"/>
+      <c r="U23" s="311"/>
+      <c r="V23" s="311"/>
+      <c r="W23" s="311"/>
+      <c r="X23" s="311"/>
+      <c r="Y23" s="311"/>
+      <c r="Z23" s="311"/>
+      <c r="AA23" s="311"/>
     </row>
     <row r="26" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="147"/>
-      <c r="B26" s="192"/>
-      <c r="C26" s="192"/>
-      <c r="D26" s="246" t="s">
+      <c r="A26" s="143"/>
+      <c r="B26" s="188"/>
+      <c r="C26" s="188"/>
+      <c r="D26" s="316" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" s="317"/>
+      <c r="F26" s="317"/>
+      <c r="G26" s="317"/>
+      <c r="H26" s="317"/>
+      <c r="I26" s="317"/>
+      <c r="J26" s="317"/>
+      <c r="K26" s="317"/>
+      <c r="L26" s="317"/>
+      <c r="M26" s="188"/>
+      <c r="N26" s="188"/>
+      <c r="O26" s="143"/>
+      <c r="P26" s="143"/>
+      <c r="Q26" s="143"/>
+      <c r="R26" s="316" t="s">
         <v>236</v>
       </c>
-      <c r="E26" s="247"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="247"/>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="247"/>
-      <c r="M26" s="192"/>
-      <c r="N26" s="192"/>
-      <c r="O26" s="147"/>
-      <c r="P26" s="147"/>
-      <c r="Q26" s="147"/>
-      <c r="R26" s="246" t="s">
+      <c r="S26" s="317"/>
+      <c r="T26" s="317"/>
+      <c r="U26" s="317"/>
+      <c r="V26" s="317"/>
+      <c r="W26" s="317"/>
+      <c r="X26" s="317"/>
+      <c r="Y26" s="317"/>
+      <c r="Z26" s="317"/>
+      <c r="AA26" s="143"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C27" s="143"/>
+      <c r="D27" s="314" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27" s="315"/>
+      <c r="F27" s="315"/>
+      <c r="G27" s="315"/>
+      <c r="H27" s="315"/>
+      <c r="I27" s="315"/>
+      <c r="J27" s="315"/>
+      <c r="K27" s="315"/>
+      <c r="L27" s="315"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="143"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="143"/>
+      <c r="Q27" s="143"/>
+      <c r="R27" s="314" t="s">
         <v>237</v>
       </c>
-      <c r="S26" s="247"/>
-      <c r="T26" s="247"/>
-      <c r="U26" s="247"/>
-      <c r="V26" s="247"/>
-      <c r="W26" s="247"/>
-      <c r="X26" s="247"/>
-      <c r="Y26" s="247"/>
-      <c r="Z26" s="247"/>
-      <c r="AA26" s="147"/>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C27" s="147"/>
-      <c r="D27" s="253" t="s">
-        <v>212</v>
-      </c>
-      <c r="E27" s="254"/>
-      <c r="F27" s="254"/>
-      <c r="G27" s="254"/>
-      <c r="H27" s="254"/>
-      <c r="I27" s="254"/>
-      <c r="J27" s="254"/>
-      <c r="K27" s="254"/>
-      <c r="L27" s="254"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="147"/>
-      <c r="P27" s="147"/>
-      <c r="Q27" s="147"/>
-      <c r="R27" s="253" t="s">
-        <v>238</v>
-      </c>
-      <c r="S27" s="254"/>
-      <c r="T27" s="254"/>
-      <c r="U27" s="254"/>
-      <c r="V27" s="254"/>
-      <c r="W27" s="254"/>
-      <c r="X27" s="254"/>
-      <c r="Y27" s="254"/>
-      <c r="Z27" s="254"/>
-      <c r="AA27" s="147"/>
+      <c r="S27" s="315"/>
+      <c r="T27" s="315"/>
+      <c r="U27" s="315"/>
+      <c r="V27" s="315"/>
+      <c r="W27" s="315"/>
+      <c r="X27" s="315"/>
+      <c r="Y27" s="315"/>
+      <c r="Z27" s="315"/>
+      <c r="AA27" s="143"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="250" t="s">
+      <c r="D28" s="325" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
-      <c r="I28" s="251"/>
-      <c r="J28" s="251"/>
-      <c r="K28" s="251"/>
-      <c r="L28" s="251"/>
-      <c r="R28" s="250"/>
-      <c r="S28" s="251"/>
-      <c r="T28" s="251"/>
-      <c r="U28" s="251"/>
-      <c r="V28" s="251"/>
-      <c r="W28" s="251"/>
-      <c r="X28" s="251"/>
-      <c r="Y28" s="251"/>
-      <c r="Z28" s="251"/>
+      <c r="E28" s="319"/>
+      <c r="F28" s="319"/>
+      <c r="G28" s="319"/>
+      <c r="H28" s="319"/>
+      <c r="I28" s="319"/>
+      <c r="J28" s="319"/>
+      <c r="K28" s="319"/>
+      <c r="L28" s="319"/>
+      <c r="R28" s="325"/>
+      <c r="S28" s="319"/>
+      <c r="T28" s="319"/>
+      <c r="U28" s="319"/>
+      <c r="V28" s="319"/>
+      <c r="W28" s="319"/>
+      <c r="X28" s="319"/>
+      <c r="Y28" s="319"/>
+      <c r="Z28" s="319"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="248" t="s">
+      <c r="D29" s="299" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="242"/>
-      <c r="F29" s="242"/>
-      <c r="G29" s="242"/>
-      <c r="H29" s="242"/>
-      <c r="I29" s="242"/>
-      <c r="J29" s="242"/>
-      <c r="K29" s="242"/>
-      <c r="L29" s="242"/>
-      <c r="P29" s="164"/>
-      <c r="Q29" s="164"/>
-      <c r="R29" s="164"/>
-      <c r="S29" s="164"/>
-      <c r="T29" s="164"/>
-      <c r="U29" s="164"/>
-      <c r="V29" s="164"/>
-      <c r="W29" s="164"/>
-      <c r="X29" s="164"/>
-      <c r="Y29" s="164"/>
-      <c r="Z29" s="164"/>
-      <c r="AA29" s="164"/>
+      <c r="E29" s="311"/>
+      <c r="F29" s="311"/>
+      <c r="G29" s="311"/>
+      <c r="H29" s="311"/>
+      <c r="I29" s="311"/>
+      <c r="J29" s="311"/>
+      <c r="K29" s="311"/>
+      <c r="L29" s="311"/>
+      <c r="P29" s="160"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="160"/>
+      <c r="S29" s="160"/>
+      <c r="T29" s="160"/>
+      <c r="U29" s="160"/>
+      <c r="V29" s="160"/>
+      <c r="W29" s="160"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="160"/>
+      <c r="Z29" s="160"/>
+      <c r="AA29" s="160"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C30" s="158"/>
-      <c r="D30" s="158" t="s">
+      <c r="C30" s="154"/>
+      <c r="D30" s="154" t="s">
         <v>215</v>
       </c>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="P30" s="164"/>
-      <c r="Q30" s="164"/>
-      <c r="R30" s="164"/>
-      <c r="S30" s="164"/>
-      <c r="T30" s="164"/>
-      <c r="U30" s="164"/>
-      <c r="V30" s="164"/>
-      <c r="W30" s="164"/>
-      <c r="X30" s="164"/>
-      <c r="Y30" s="164"/>
-      <c r="Z30" s="164"/>
-      <c r="AA30" s="164"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="P30" s="160"/>
+      <c r="Q30" s="160"/>
+      <c r="R30" s="160"/>
+      <c r="S30" s="160"/>
+      <c r="T30" s="160"/>
+      <c r="U30" s="160"/>
+      <c r="V30" s="160"/>
+      <c r="W30" s="160"/>
+      <c r="X30" s="160"/>
+      <c r="Y30" s="160"/>
+      <c r="Z30" s="160"/>
+      <c r="AA30" s="160"/>
     </row>
     <row r="31" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="164"/>
-      <c r="D31" s="193"/>
-      <c r="E31" s="194" t="s">
+      <c r="C31" s="160"/>
+      <c r="D31" s="189"/>
+      <c r="E31" s="190" t="s">
         <v>216</v>
       </c>
-      <c r="F31" s="193"/>
-      <c r="G31" s="193"/>
-      <c r="H31" s="193"/>
-      <c r="I31" s="193"/>
-      <c r="J31" s="193"/>
-      <c r="K31" s="193"/>
-      <c r="L31" s="193"/>
-      <c r="P31" s="164"/>
-      <c r="Q31" s="164"/>
-      <c r="R31" s="164"/>
-      <c r="S31" s="164"/>
-      <c r="T31" s="164"/>
-      <c r="U31" s="164"/>
-      <c r="V31" s="164"/>
-      <c r="W31" s="164"/>
-      <c r="X31" s="164"/>
-      <c r="Y31" s="164"/>
-      <c r="Z31" s="164"/>
-      <c r="AA31" s="164"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="189"/>
+      <c r="I31" s="189"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="189"/>
+      <c r="L31" s="189"/>
+      <c r="P31" s="160"/>
+      <c r="Q31" s="160"/>
+      <c r="R31" s="160"/>
+      <c r="S31" s="160"/>
+      <c r="T31" s="160"/>
+      <c r="U31" s="160"/>
+      <c r="V31" s="160"/>
+      <c r="W31" s="160"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="160"/>
+      <c r="Z31" s="160"/>
+      <c r="AA31" s="160"/>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B32" s="164"/>
-      <c r="C32" s="164"/>
-      <c r="D32" s="164"/>
-      <c r="E32" s="144" t="s">
+      <c r="B32" s="160"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="140" t="s">
         <v>217</v>
       </c>
-      <c r="F32" s="164"/>
-      <c r="H32" s="144"/>
-      <c r="P32" s="164"/>
-      <c r="Q32" s="164"/>
-      <c r="R32" s="164"/>
-      <c r="S32" s="164"/>
-      <c r="T32" s="164"/>
-      <c r="U32" s="164"/>
-      <c r="V32" s="164"/>
-      <c r="W32" s="164"/>
-      <c r="X32" s="164"/>
-      <c r="Y32" s="164"/>
-      <c r="Z32" s="164"/>
-      <c r="AA32" s="164"/>
+      <c r="F32" s="160"/>
+      <c r="H32" s="140"/>
+      <c r="P32" s="160"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="160"/>
+      <c r="T32" s="160"/>
+      <c r="U32" s="160"/>
+      <c r="V32" s="160"/>
+      <c r="W32" s="160"/>
+      <c r="X32" s="160"/>
+      <c r="Y32" s="160"/>
+      <c r="Z32" s="160"/>
+      <c r="AA32" s="160"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B33" s="164"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="164"/>
-      <c r="H33" s="144"/>
-      <c r="P33" s="164"/>
-      <c r="Q33" s="164"/>
-      <c r="R33" s="164"/>
-      <c r="S33" s="164"/>
-      <c r="T33" s="164"/>
-      <c r="U33" s="164"/>
-      <c r="V33" s="164"/>
-      <c r="W33" s="164"/>
-      <c r="X33" s="164"/>
-      <c r="Y33" s="164"/>
-      <c r="Z33" s="164"/>
-      <c r="AA33" s="164"/>
+      <c r="B33" s="160"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="160"/>
+      <c r="H33" s="140"/>
+      <c r="P33" s="160"/>
+      <c r="Q33" s="160"/>
+      <c r="R33" s="160"/>
+      <c r="S33" s="160"/>
+      <c r="T33" s="160"/>
+      <c r="U33" s="160"/>
+      <c r="V33" s="160"/>
+      <c r="W33" s="160"/>
+      <c r="X33" s="160"/>
+      <c r="Y33" s="160"/>
+      <c r="Z33" s="160"/>
+      <c r="AA33" s="160"/>
     </row>
     <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="248" t="s">
+      <c r="A34" s="299" t="s">
         <v>218</v>
       </c>
-      <c r="B34" s="242"/>
-      <c r="C34" s="242"/>
-      <c r="D34" s="242"/>
-      <c r="E34" s="242"/>
-      <c r="F34" s="242"/>
-      <c r="G34" s="195"/>
-      <c r="H34" s="164" t="s">
+      <c r="B34" s="311"/>
+      <c r="C34" s="311"/>
+      <c r="D34" s="311"/>
+      <c r="E34" s="311"/>
+      <c r="F34" s="311"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="160" t="s">
         <v>219</v>
       </c>
-      <c r="I34" s="249" t="s">
+      <c r="I34" s="324" t="s">
+        <v>233</v>
+      </c>
+      <c r="J34" s="317"/>
+      <c r="K34" s="317"/>
+      <c r="L34" s="317"/>
+      <c r="M34" s="317"/>
+      <c r="N34" s="317"/>
+      <c r="O34" s="160" t="s">
+        <v>220</v>
+      </c>
+      <c r="P34" s="322" t="s">
         <v>234</v>
       </c>
-      <c r="J34" s="247"/>
-      <c r="K34" s="247"/>
-      <c r="L34" s="247"/>
-      <c r="M34" s="247"/>
-      <c r="N34" s="247"/>
-      <c r="O34" s="164" t="s">
-        <v>220</v>
-      </c>
-      <c r="P34" s="244" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q34" s="244"/>
-      <c r="R34" s="244"/>
-      <c r="S34" s="244"/>
-      <c r="T34" s="244"/>
-      <c r="U34" s="182"/>
-      <c r="V34" s="193"/>
-      <c r="W34" s="193"/>
-      <c r="X34" s="193"/>
-      <c r="Y34" s="193"/>
-      <c r="Z34" s="193"/>
-      <c r="AA34" s="193"/>
+      <c r="Q34" s="322"/>
+      <c r="R34" s="322"/>
+      <c r="S34" s="322"/>
+      <c r="T34" s="322"/>
+      <c r="U34" s="178"/>
+      <c r="V34" s="189"/>
+      <c r="W34" s="189"/>
+      <c r="X34" s="189"/>
+      <c r="Y34" s="189"/>
+      <c r="Z34" s="189"/>
+      <c r="AA34" s="189"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="V36" s="196"/>
-      <c r="W36" s="196"/>
-      <c r="X36" s="196"/>
-      <c r="Y36" s="196"/>
-      <c r="Z36" s="196"/>
-      <c r="AA36" s="196"/>
+      <c r="V36" s="192"/>
+      <c r="W36" s="192"/>
+      <c r="X36" s="192"/>
+      <c r="Y36" s="192"/>
+      <c r="Z36" s="192"/>
+      <c r="AA36" s="192"/>
     </row>
     <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="255"/>
-      <c r="K37" s="247"/>
-      <c r="L37" s="247"/>
-      <c r="M37" s="247"/>
-      <c r="N37" s="247"/>
-      <c r="O37" s="247"/>
-      <c r="P37" s="247"/>
-      <c r="Q37" s="247"/>
-      <c r="R37" s="247"/>
-      <c r="S37" s="247"/>
-      <c r="T37" s="147"/>
-      <c r="U37" s="147"/>
-      <c r="V37" s="147"/>
-      <c r="W37" s="147"/>
-      <c r="X37" s="147"/>
-      <c r="Y37" s="147"/>
-      <c r="Z37" s="147"/>
-      <c r="AA37" s="147"/>
+      <c r="J37" s="327"/>
+      <c r="K37" s="317"/>
+      <c r="L37" s="317"/>
+      <c r="M37" s="317"/>
+      <c r="N37" s="317"/>
+      <c r="O37" s="317"/>
+      <c r="P37" s="317"/>
+      <c r="Q37" s="317"/>
+      <c r="R37" s="317"/>
+      <c r="S37" s="317"/>
+      <c r="T37" s="143"/>
+      <c r="U37" s="143"/>
+      <c r="V37" s="143"/>
+      <c r="W37" s="143"/>
+      <c r="X37" s="143"/>
+      <c r="Y37" s="143"/>
+      <c r="Z37" s="143"/>
+      <c r="AA37" s="143"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="253" t="s">
+      <c r="J38" s="314" t="s">
         <v>221</v>
       </c>
-      <c r="K38" s="254"/>
-      <c r="L38" s="254"/>
-      <c r="M38" s="254"/>
-      <c r="N38" s="254"/>
-      <c r="O38" s="254"/>
-      <c r="P38" s="254"/>
-      <c r="Q38" s="254"/>
-      <c r="R38" s="254"/>
-      <c r="S38" s="254"/>
-      <c r="T38" s="147"/>
-      <c r="U38" s="147"/>
-      <c r="V38" s="147"/>
-      <c r="W38" s="147"/>
-      <c r="X38" s="147"/>
-      <c r="Y38" s="147"/>
-      <c r="Z38" s="147"/>
-      <c r="AA38" s="147"/>
+      <c r="K38" s="315"/>
+      <c r="L38" s="315"/>
+      <c r="M38" s="315"/>
+      <c r="N38" s="315"/>
+      <c r="O38" s="315"/>
+      <c r="P38" s="315"/>
+      <c r="Q38" s="315"/>
+      <c r="R38" s="315"/>
+      <c r="S38" s="315"/>
+      <c r="T38" s="143"/>
+      <c r="U38" s="143"/>
+      <c r="V38" s="143"/>
+      <c r="W38" s="143"/>
+      <c r="X38" s="143"/>
+      <c r="Y38" s="143"/>
+      <c r="Z38" s="143"/>
+      <c r="AA38" s="143"/>
     </row>
     <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="245" t="s">
+      <c r="A40" s="323" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="242"/>
-      <c r="C40" s="242"/>
-      <c r="D40" s="243" t="s">
+      <c r="B40" s="311"/>
+      <c r="C40" s="311"/>
+      <c r="D40" s="321" t="s">
         <v>223</v>
       </c>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
-      <c r="M40" s="242"/>
-      <c r="N40" s="242"/>
-      <c r="O40" s="242"/>
-      <c r="P40" s="242"/>
-      <c r="Q40" s="242"/>
-      <c r="R40" s="242"/>
-      <c r="S40" s="242"/>
-      <c r="T40" s="242"/>
-      <c r="U40" s="242"/>
-      <c r="V40" s="242"/>
-      <c r="W40" s="242"/>
-      <c r="X40" s="242"/>
-      <c r="Y40" s="242"/>
-      <c r="Z40" s="242"/>
-      <c r="AA40" s="242"/>
+      <c r="E40" s="311"/>
+      <c r="F40" s="311"/>
+      <c r="G40" s="311"/>
+      <c r="H40" s="311"/>
+      <c r="I40" s="311"/>
+      <c r="J40" s="311"/>
+      <c r="K40" s="311"/>
+      <c r="L40" s="311"/>
+      <c r="M40" s="311"/>
+      <c r="N40" s="311"/>
+      <c r="O40" s="311"/>
+      <c r="P40" s="311"/>
+      <c r="Q40" s="311"/>
+      <c r="R40" s="311"/>
+      <c r="S40" s="311"/>
+      <c r="T40" s="311"/>
+      <c r="U40" s="311"/>
+      <c r="V40" s="311"/>
+      <c r="W40" s="311"/>
+      <c r="X40" s="311"/>
+      <c r="Y40" s="311"/>
+      <c r="Z40" s="311"/>
+      <c r="AA40" s="311"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="J41" s="144"/>
-      <c r="K41" s="144"/>
-      <c r="L41" s="144"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="140"/>
+      <c r="J41" s="140"/>
+      <c r="K41" s="140"/>
+      <c r="L41" s="140"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C42" s="191"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="191"/>
-      <c r="F42" s="191"/>
-      <c r="G42" s="191"/>
-      <c r="H42" s="191"/>
-      <c r="J42" s="191"/>
-      <c r="K42" s="191"/>
-      <c r="L42" s="191"/>
-      <c r="M42" s="144"/>
-      <c r="N42" s="144"/>
-      <c r="O42" s="144"/>
-      <c r="AA42" s="144"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="187"/>
+      <c r="L42" s="187"/>
+      <c r="M42" s="140"/>
+      <c r="N42" s="140"/>
+      <c r="O42" s="140"/>
+      <c r="AA42" s="140"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="144"/>
-      <c r="I43" s="144"/>
-      <c r="M43" s="191"/>
-      <c r="N43" s="191"/>
-      <c r="O43" s="191"/>
-      <c r="AA43" s="191"/>
+      <c r="A43" s="140"/>
+      <c r="I43" s="140"/>
+      <c r="M43" s="187"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="187"/>
+      <c r="AA43" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="R27:Z27"/>
-    <mergeCell ref="R26:Z26"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="R6:Z9"/>
-    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D40:AA40"/>
     <mergeCell ref="P34:T34"/>
@@ -8023,6 +8067,12 @@
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R27:Z27"/>
+    <mergeCell ref="R26:Z26"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="R6:Z9"/>
+    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -8036,96 +8086,96 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="29" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D29" s="197"/>
-      <c r="E29" s="198"/>
-      <c r="F29" s="198"/>
-      <c r="G29" s="198"/>
-      <c r="H29" s="198"/>
-      <c r="I29" s="198"/>
-      <c r="J29" s="198"/>
-      <c r="K29" s="199"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="194"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="194"/>
+      <c r="I29" s="194"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="195"/>
     </row>
     <row r="30" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D30" s="200"/>
-      <c r="E30" s="336" t="s">
+      <c r="D30" s="196"/>
+      <c r="E30" s="332" t="s">
         <v>224</v>
       </c>
-      <c r="F30" s="333"/>
-      <c r="G30" s="333"/>
-      <c r="H30" s="333"/>
-      <c r="I30" s="333"/>
-      <c r="J30" s="333"/>
-      <c r="K30" s="292"/>
+      <c r="F30" s="329"/>
+      <c r="G30" s="329"/>
+      <c r="H30" s="329"/>
+      <c r="I30" s="329"/>
+      <c r="J30" s="329"/>
+      <c r="K30" s="261"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D31" s="200"/>
-      <c r="K31" s="201"/>
+      <c r="D31" s="196"/>
+      <c r="K31" s="197"/>
     </row>
     <row r="32" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D32" s="200"/>
-      <c r="E32" s="202"/>
-      <c r="F32" s="335" t="s">
+      <c r="D32" s="196"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="331" t="s">
         <v>225</v>
       </c>
-      <c r="G32" s="333"/>
-      <c r="H32" s="333"/>
-      <c r="I32" s="333"/>
-      <c r="J32" s="333"/>
-      <c r="K32" s="292"/>
+      <c r="G32" s="329"/>
+      <c r="H32" s="329"/>
+      <c r="I32" s="329"/>
+      <c r="J32" s="329"/>
+      <c r="K32" s="261"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D33" s="200"/>
-      <c r="K33" s="201"/>
+      <c r="D33" s="196"/>
+      <c r="K33" s="197"/>
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D34" s="200"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="332" t="s">
+      <c r="D34" s="196"/>
+      <c r="E34" s="199"/>
+      <c r="F34" s="328" t="s">
         <v>226</v>
       </c>
-      <c r="G34" s="333"/>
-      <c r="H34" s="333"/>
-      <c r="I34" s="333"/>
-      <c r="J34" s="333"/>
-      <c r="K34" s="292"/>
+      <c r="G34" s="329"/>
+      <c r="H34" s="329"/>
+      <c r="I34" s="329"/>
+      <c r="J34" s="329"/>
+      <c r="K34" s="261"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D35" s="200"/>
-      <c r="K35" s="201"/>
+      <c r="D35" s="196"/>
+      <c r="K35" s="197"/>
     </row>
     <row r="36" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D36" s="200"/>
-      <c r="E36" s="204"/>
-      <c r="F36" s="337" t="s">
+      <c r="D36" s="196"/>
+      <c r="E36" s="200"/>
+      <c r="F36" s="333" t="s">
         <v>227</v>
       </c>
-      <c r="G36" s="333"/>
-      <c r="H36" s="333"/>
-      <c r="I36" s="333"/>
-      <c r="J36" s="333"/>
-      <c r="K36" s="201"/>
+      <c r="G36" s="329"/>
+      <c r="H36" s="329"/>
+      <c r="I36" s="329"/>
+      <c r="J36" s="329"/>
+      <c r="K36" s="197"/>
     </row>
     <row r="37" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D37" s="205"/>
-      <c r="E37" s="206"/>
-      <c r="F37" s="206"/>
-      <c r="G37" s="206"/>
-      <c r="H37" s="206"/>
-      <c r="I37" s="206"/>
-      <c r="J37" s="206"/>
-      <c r="K37" s="207"/>
+      <c r="D37" s="201"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="202"/>
+      <c r="I37" s="202"/>
+      <c r="J37" s="202"/>
+      <c r="K37" s="203"/>
     </row>
     <row r="39" spans="4:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="334" t="s">
+      <c r="D39" s="330" t="s">
         <v>228</v>
       </c>
-      <c r="E39" s="333"/>
-      <c r="F39" s="333"/>
-      <c r="G39" s="333"/>
-      <c r="H39" s="333"/>
-      <c r="I39" s="333"/>
-      <c r="J39" s="333"/>
-      <c r="K39" s="333"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
+      <c r="G39" s="329"/>
+      <c r="H39" s="329"/>
+      <c r="I39" s="329"/>
+      <c r="J39" s="329"/>
+      <c r="K39" s="329"/>
     </row>
   </sheetData>
   <mergeCells count="5">
